--- a/public/downloads/engine-workshop-template.xlsx
+++ b/public/downloads/engine-workshop-template.xlsx
@@ -131,6 +131,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,7 +141,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
@@ -243,6 +243,36 @@
     <author>Mogi</author>
   </authors>
   <commentList>
+    <comment ref="F13" authorId="0" shapeId="0">
+      <text>
+        <t>דוגמה: ההחזר הראשון של האומדן. לכל מסלול: ROUND(-PMT(ריבית מהמחירון/1200, חודשים, סכום), 2); אין חלק, אין החזר</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>אותו חישוב כמו ב־F13, אבל עם הריביות של ההצעה (F9 עד F11) במקום המחירון</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>הצעה פחות אומדן: =F14-F13. מינוס אומר שההצעה זולה מהאומדן</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>אותו חישוב כמו ב־F13 בלי ROUND, כפול מספר החודשים</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>אותו חישוב כמו ב־F16, עם הריביות של ההצעה</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>הצעה פחות אומדן: =F17-F16</t>
+      </text>
+    </comment>
     <comment ref="E88" authorId="0" shapeId="0">
       <text>
         <t>סכום המסלול = ההלוואה × החלק ÷ 100, מעוגל לאגורה: =ROUND($B$47*B{r}/100,2)</t>
@@ -805,7 +835,10 @@
           <t>אומדן: ההחזר הראשון (₪)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="n"/>
+      <c r="F13" s="10">
+        <f>IF($F$6&gt;0,ROUND(-PMT(INDEX($C$28:$C$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$6/100,2)),2),0)+IF($F$7&gt;0,ROUND(-PMT(INDEX($D$28:$D$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$7/100,2)),2),0)+IF($F$8&gt;0,ROUND(-PMT(INDEX($E$28:$E$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$8/100,2)),2),0)</f>
+        <v>8310.78</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -821,7 +854,7 @@
           <t>הצעה: ההחזר הראשון (₪)</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
+      <c r="F14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -829,7 +862,7 @@
           <t>יעד יחס ההחזר של הלקוח (%)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -837,7 +870,7 @@
           <t>הפער בהחזר הראשון (₪)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n"/>
+      <c r="F15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="E16" s="4" t="inlineStr">
@@ -845,7 +878,7 @@
           <t>אומדן: סך התשלומים (₪)</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
+      <c r="F16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -858,7 +891,7 @@
           <t>הצעה: סך התשלומים (₪)</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -879,7 +912,7 @@
           <t>הפער בסך התשלומים (₪)</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -907,7 +940,7 @@
           <t>בנק (a, b, c או d)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -961,147 +994,147 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>קוד</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>שם</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>קבועה</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>פריים</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>משתנה</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>סירוב ביחס החזר (%)</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>סירוב בשיעור מימון (%)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>בנק א׳</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>4.4</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>4.6</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>4.1</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="15" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>בנק ב׳</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="15" t="n">
         <v>4.3</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>4.7</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="14" t="n">
+      <c r="G29" s="15" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>בנק ג׳</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="15" t="n">
         <v>4.35</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="15" t="n">
         <v>4.55</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="15" t="n">
         <v>4.2</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="G30" s="15" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>בנק ד׳</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="15" t="n">
         <v>4.45</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="15" t="n">
         <v>4.65</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="15" t="n">
         <v>4.15</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G31" s="14" t="n">
+      <c r="G31" s="15" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1118,7 +1151,7 @@
           <t>תקרת שיעור מימון (%)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B34" s="16" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1128,7 +1161,7 @@
           <t>תקרת יחס ההחזר (%)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B35" s="16" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1138,7 +1171,7 @@
           <t>החלק המרבי בריבית משתנה: מונה</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1148,7 +1181,7 @@
           <t>החלק המרבי בריבית משתנה: מכנה</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1158,7 +1191,7 @@
           <t>התקופה המרבית (חודשים)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>360</v>
       </c>
     </row>
@@ -1168,7 +1201,7 @@
           <t>התקופה של כל מסלול בחיפוש (חודשים)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>360</v>
       </c>
     </row>
@@ -1178,7 +1211,7 @@
           <t>תרחיש לחץ: פריים עולה (נקודות אחוז, מהשנה השנייה)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1188,7 +1221,7 @@
           <t>תרחיש לחץ: העוגן עולה בעדכון (נקודות אחוז)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1198,7 +1231,7 @@
           <t>חודשים בין עדכוני הריבית במסלול משתנה</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1215,7 +1248,7 @@
           <t>ההון העצמי שנכנס לעסקה (₪)</t>
         </is>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="10">
         <f>$B$6+$B$18</f>
         <v>580000</v>
       </c>
@@ -1226,7 +1259,7 @@
           <t>ההון העצמי הזמין (₪)</t>
         </is>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="10">
         <f>$B$6+MAX($B$7-IF($B$19=1,$B$8,0),0)</f>
         <v>600000</v>
       </c>
@@ -1237,7 +1270,7 @@
           <t>סכום ההלוואה (₪)</t>
         </is>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="10">
         <f>$B$5-$B$45</f>
         <v>1620000</v>
       </c>
@@ -1248,7 +1281,7 @@
           <t>שיעור מימון (%)</t>
         </is>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="16">
         <f>$B$47/$B$5*100</f>
         <v>73.6363636363636</v>
       </c>
@@ -1259,7 +1292,7 @@
           <t>הכנסה מוכרת (₪)</t>
         </is>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="10">
         <f>$B$11+$B$12+IF($B$20=1,$B$13,0)</f>
         <v>21700</v>
       </c>
@@ -1270,7 +1303,7 @@
           <t>הלוואת הרכב נספרת בחישוב (₪, כשנשארו מעל 18 חודשים)</t>
         </is>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="10">
         <f>IF(AND($B$19=0,$B$10&gt;18),$B$9,0)</f>
         <v>1450</v>
       </c>
@@ -1281,7 +1314,7 @@
           <t>הכנסה פנויה (₪)</t>
         </is>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="10">
         <f>$B$49-$B$50</f>
         <v>20250</v>
       </c>
@@ -1292,7 +1325,7 @@
           <t>מחירון הבנק: קבועה (%)</t>
         </is>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="16">
         <f>INDEX($C$28:$C$31,MATCH($B$21,$A$28:$A$31,0))</f>
         <v>4.4</v>
       </c>
@@ -1303,7 +1336,7 @@
           <t>מחירון הבנק: פריים (%)</t>
         </is>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="16">
         <f>INDEX($D$28:$D$31,MATCH($B$21,$A$28:$A$31,0))</f>
         <v>4.6</v>
       </c>
@@ -1314,7 +1347,7 @@
           <t>מחירון הבנק: משתנה (%)</t>
         </is>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="16">
         <f>INDEX($E$28:$E$31,MATCH($B$21,$A$28:$A$31,0))</f>
         <v>4.1</v>
       </c>
@@ -1325,7 +1358,7 @@
           <t>קו הסירוב של הבנק ביחס החזר (%)</t>
         </is>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="16">
         <f>INDEX($F$28:$F$31,MATCH($B$21,$A$28:$A$31,0))</f>
         <v>45</v>
       </c>
@@ -1336,7 +1369,7 @@
           <t>קו הסירוב של הבנק בשיעור מימון (%)</t>
         </is>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="16">
         <f>INDEX($G$28:$G$31,MATCH($B$21,$A$28:$A$31,0))</f>
         <v>75</v>
       </c>
@@ -1354,7 +1387,7 @@
           <t>כמה מועמדים ברשת</t>
         </is>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="17">
         <f>COUNTA($A$89:$A$154)</f>
         <v>66</v>
       </c>
@@ -1365,7 +1398,7 @@
           <t>כמה מהם אפשריים</t>
         </is>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="17">
         <f>SUM($AC$89:$AC$154)</f>
         <v>0</v>
       </c>
@@ -1376,7 +1409,7 @@
           <t>כמה מהם יעילים</t>
         </is>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <f>SUM($AE$89:$AE$154)</f>
         <v>0</v>
       </c>
@@ -1398,7 +1431,7 @@
           <t>ההחזר הראשון שלו (₪)</t>
         </is>
       </c>
-      <c r="B63" s="17" t="str">
+      <c r="B63" s="10" t="str">
         <f>IFERROR(INDEX($K$89:$K$154,MATCH(1,$AM$89:$AM$154,0)),"")</f>
         <v/>
       </c>
@@ -1409,7 +1442,7 @@
           <t>סך התשלומים שלו (₪)</t>
         </is>
       </c>
-      <c r="B64" s="17" t="str">
+      <c r="B64" s="10" t="str">
         <f>IFERROR(INDEX($M$89:$M$154,MATCH(1,$AM$89:$AM$154,0)),"")</f>
         <v/>
       </c>
@@ -1420,7 +1453,7 @@
           <t>החשיפה שלו (₪)</t>
         </is>
       </c>
-      <c r="B65" s="17" t="str">
+      <c r="B65" s="10" t="str">
         <f>IFERROR(INDEX($O$89:$O$154,MATCH(1,$AM$89:$AM$154,0)),"")</f>
         <v/>
       </c>
@@ -1442,7 +1475,7 @@
           <t>ההפרש בהחזר הראשון: השני פחות הנבחר (₪)</t>
         </is>
       </c>
-      <c r="B67" s="17" t="str">
+      <c r="B67" s="10" t="str">
         <f>IFERROR(INDEX($K$89:$K$154,MATCH(2,$AM$89:$AM$154,0))-$B$63,"")</f>
         <v/>
       </c>
@@ -1453,7 +1486,7 @@
           <t>ההפרש בסך התשלומים (₪)</t>
         </is>
       </c>
-      <c r="B68" s="17" t="str">
+      <c r="B68" s="10" t="str">
         <f>IFERROR(INDEX($M$89:$M$154,MATCH(2,$AM$89:$AM$154,0))-$B$64,"")</f>
         <v/>
       </c>
@@ -1464,7 +1497,7 @@
           <t>ההפרש בחשיפה (₪)</t>
         </is>
       </c>
-      <c r="B69" s="17" t="str">
+      <c r="B69" s="10" t="str">
         <f>IFERROR(INDEX($O$89:$O$154,MATCH(2,$AM$89:$AM$154,0))-$B$65,"")</f>
         <v/>
       </c>
@@ -1604,11 +1637,11 @@
           <t>ההסבר, מתוך המספרים בלבד</t>
         </is>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="10">
         <f>IF(COUNT($AF$89:$AF$154)=0,MIN($K$89:$K$154),MIN($AF$89:$AF$154))</f>
         <v>7827.81</v>
       </c>
-      <c r="C83" s="17">
+      <c r="C83" s="10">
         <f>IF(COUNT($AF$89:$AF$154)=0,MAX($K$89:$K$154),MAX($AF$89:$AF$154))</f>
         <v>7827.81</v>
       </c>
@@ -1618,11 +1651,11 @@
         <f>IF(ISNUMBER($B$63),"נבחר תמהיל "&amp;INDEX($B$89:$B$154,MATCH(1,$AM$89:$AM$154,0))&amp;"% קבועה, "&amp;INDEX($C$89:$C$154,MATCH(1,$AM$89:$AM$154,0))&amp;"% פריים ו־"&amp;INDEX($D$89:$D$154,MATCH(1,$AM$89:$AM$154,0))&amp;"% משתנה. ההחזר הראשון "&amp;TEXT($B$63,"#,##0.00")&amp;" ₪, סך התשלומים "&amp;TEXT($B$64,"#,##0")&amp;" ₪, החשיפה "&amp;TEXT($B$65,"#,##0.00")&amp;" ₪.","אף מועמד לא עבר את כל האילוצים: שנו את הבחירות.")</f>
         <v>אף מועמד לא עבר את כל האילוצים: שנו את הבחירות.</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="10">
         <f>IF(COUNT($AG$89:$AG$154)=0,MIN($M$89:$M$154),MIN($AG$89:$AG$154))</f>
         <v>2818012.90026971</v>
       </c>
-      <c r="C84" s="17">
+      <c r="C84" s="10">
         <f>IF(COUNT($AG$89:$AG$154)=0,MAX($M$89:$M$154),MAX($AG$89:$AG$154))</f>
         <v>2818012.90026971</v>
       </c>
@@ -1632,11 +1665,11 @@
         <f>"נפסלו "&amp;($B$59-$B$60)&amp;" מתוך "&amp;$B$59&amp;" מועמדים. מתוך האפשריים "&amp;$B$61&amp;" יעילים: לא ניתן לשפר בהם מדד בלי לפגוע באחר."</f>
         <v>נפסלו 66 מתוך 66 מועמדים. מתוך האפשריים 0 יעילים: לא ניתן לשפר בהם מדד בלי לפגוע באחר.</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="10">
         <f>IF(COUNT($AH$89:$AH$154)=0,MIN($O$89:$O$154),MIN($AH$89:$AH$154))</f>
         <v>1717.89182275674</v>
       </c>
-      <c r="C85" s="17">
+      <c r="C85" s="10">
         <f>IF(COUNT($AH$89:$AH$154)=0,MAX($O$89:$O$154),MAX($AH$89:$AH$154))</f>
         <v>1717.89182275674</v>
       </c>
@@ -1867,123 +1900,123 @@
       <c r="D89" t="n">
         <v>100</v>
       </c>
-      <c r="E89" s="17">
+      <c r="E89" s="10">
         <f>ROUND($B$47*B89/100,2)</f>
         <v>0</v>
       </c>
-      <c r="F89" s="17">
+      <c r="F89" s="10">
         <f>ROUND($B$47*C89/100,2)</f>
         <v>0</v>
       </c>
-      <c r="G89" s="17">
+      <c r="G89" s="10">
         <f>ROUND($B$47*D89/100,2)</f>
         <v>1620000</v>
       </c>
-      <c r="H89" s="17">
+      <c r="H89" s="10">
         <f>IF(E89&gt;0,ROUND(-PMT($B$52/1200,$B$39,E89),2),0)</f>
         <v>0</v>
       </c>
-      <c r="I89" s="17">
+      <c r="I89" s="10">
         <f>IF(F89&gt;0,ROUND(-PMT($B$53/1200,$B$39,F89),2),0)</f>
         <v>0</v>
       </c>
-      <c r="J89" s="17">
+      <c r="J89" s="10">
         <f>IF(G89&gt;0,ROUND(-PMT($B$54/1200,$B$39,G89),2),0)</f>
         <v>7827.81</v>
       </c>
-      <c r="K89" s="17">
+      <c r="K89" s="10">
         <f>H89+I89+J89</f>
         <v>7827.81</v>
       </c>
-      <c r="L89" s="17">
+      <c r="L89" s="10">
         <f>IF(E89&gt;0,-PMT($B$52/1200,$B$39,E89),0)+IF(F89&gt;0,-PMT($B$53/1200,$B$39,F89),0)+IF(G89&gt;0,-PMT($B$54/1200,$B$39,G89),0)</f>
         <v>7827.8136118603</v>
       </c>
-      <c r="M89" s="17">
+      <c r="M89" s="10">
         <f>L89*$B$39</f>
         <v>2818012.90026971</v>
       </c>
-      <c r="N89" s="17">
+      <c r="N89" s="10">
         <f>IF(E89&gt;0,-PMT($B$52/1200,$B$39,E89),0)+IF(F89&gt;0,-PMT(($B$53+$B$40)/1200,$B$39-12,F89*((1+$B$53/1200)^$B$39-(1+$B$53/1200)^12)/((1+$B$53/1200)^$B$39-1)),0)+IF(G89&gt;0,-PMT(($B$54+$B$41)/1200,$B$39-$B$42,G89*((1+$B$54/1200)^$B$39-(1+$B$54/1200)^$B$42)/((1+$B$54/1200)^$B$39-1)),0)</f>
         <v>9545.70182275674</v>
       </c>
-      <c r="O89" s="17">
+      <c r="O89" s="10">
         <f>N89-K89</f>
         <v>1717.89182275674</v>
       </c>
-      <c r="P89" s="15">
+      <c r="P89" s="16">
         <f>C89+D89</f>
         <v>100</v>
       </c>
-      <c r="Q89" s="15">
+      <c r="Q89" s="16">
         <f>IF($B$51&gt;0,L89/$B$51*100,1000000)</f>
         <v>38.655869688199</v>
       </c>
-      <c r="R89" s="16">
+      <c r="R89" s="17">
         <f>IF(ABS(E89+F89+G89-$B$47)&gt;0.005,1,0)</f>
         <v>0</v>
       </c>
-      <c r="S89" s="16">
+      <c r="S89" s="17">
         <f>IF($B$45&gt;$B$46,1,0)</f>
         <v>0</v>
       </c>
-      <c r="T89" s="16">
+      <c r="T89" s="17">
         <f>IF($B$48&gt;$B$34,1,0)</f>
         <v>0</v>
       </c>
-      <c r="U89" s="16">
+      <c r="U89" s="17">
         <f>IF(Q89&gt;$B$35,1,0)</f>
         <v>0</v>
       </c>
-      <c r="V89" s="16">
+      <c r="V89" s="17">
         <f>IF((F89+G89)*$B$37&gt;$B$47*$B$36,1,0)</f>
         <v>1</v>
       </c>
-      <c r="W89" s="16">
+      <c r="W89" s="17">
         <f>IF($B$39&gt;$B$38,1,0)</f>
         <v>0</v>
       </c>
-      <c r="X89" s="16">
+      <c r="X89" s="17">
         <f>IF(Q89&gt;$B$55,1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y89" s="16">
+      <c r="Y89" s="17">
         <f>IF($B$48&gt;$B$56,1,0)</f>
         <v>0</v>
       </c>
-      <c r="Z89" s="16">
+      <c r="Z89" s="17">
         <f>IF(L89&gt;$B$14,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AA89" s="16">
+      <c r="AA89" s="17">
         <f>IF(Q89&gt;$B$15,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AB89" s="16">
+      <c r="AB89" s="17">
         <f>SUM(R89:AA89)</f>
         <v>1</v>
       </c>
-      <c r="AC89" s="16">
+      <c r="AC89" s="17">
         <f>IF(AB89=0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AD89" s="16" t="str">
+      <c r="AD89" s="17" t="str">
         <f>IF(AC89=1,SUMPRODUCT(($AC$89:$AC$154=1)*($K$89:$K$154&lt;=K89)*($M$89:$M$154&lt;=M89)*($O$89:$O$154&lt;=O89)*((($K$89:$K$154&lt;K89)+($M$89:$M$154&lt;M89)+($O$89:$O$154&lt;O89))&gt;0)),"")</f>
         <v/>
       </c>
-      <c r="AE89" s="16">
+      <c r="AE89" s="17">
         <f>IF(AC89=1,IF(AD89=0,1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AF89" s="17" t="str">
+      <c r="AF89" s="10" t="str">
         <f>IF(AC89=1,K89,"")</f>
         <v/>
       </c>
-      <c r="AG89" s="17" t="str">
+      <c r="AG89" s="10" t="str">
         <f>IF(AC89=1,M89,"")</f>
         <v/>
       </c>
-      <c r="AH89" s="17" t="str">
+      <c r="AH89" s="10" t="str">
         <f>IF(AC89=1,O89,"")</f>
         <v/>
       </c>
@@ -2003,7 +2036,7 @@
         <f>ROUND(($B$22*AI89+$B$23*AJ89+$B$24*AK89)/($B$22+$B$23+$B$24),9)</f>
         <v>0</v>
       </c>
-      <c r="AM89" s="16" t="str">
+      <c r="AM89" s="17" t="str">
         <f>IF(AC89=1,1+COUNTIFS($AC$89:$AC$154,1,$AL$89:$AL$154,"&lt;"&amp;AL89)+COUNTIFS($AC$88:AC88,1,$AL$88:AL88,AL89),"")</f>
         <v/>
       </c>
@@ -2023,17 +2056,17 @@
       <c r="D90" t="n">
         <v>90</v>
       </c>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
+      <c r="E90" s="11" t="n"/>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="11" t="n"/>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="11" t="n"/>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="11" t="n"/>
+      <c r="O90" s="11" t="n"/>
       <c r="P90" s="23" t="n"/>
       <c r="Q90" s="23" t="n"/>
       <c r="R90" s="24" t="n"/>
@@ -2050,9 +2083,9 @@
       <c r="AC90" s="24" t="n"/>
       <c r="AD90" s="24" t="n"/>
       <c r="AE90" s="24" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
+      <c r="AF90" s="11" t="n"/>
+      <c r="AG90" s="11" t="n"/>
+      <c r="AH90" s="11" t="n"/>
       <c r="AI90" s="25" t="n"/>
       <c r="AJ90" s="25" t="n"/>
       <c r="AK90" s="25" t="n"/>
@@ -2074,17 +2107,17 @@
       <c r="D91" t="n">
         <v>80</v>
       </c>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="O91" s="11" t="n"/>
       <c r="P91" s="23" t="n"/>
       <c r="Q91" s="23" t="n"/>
       <c r="R91" s="24" t="n"/>
@@ -2101,9 +2134,9 @@
       <c r="AC91" s="24" t="n"/>
       <c r="AD91" s="24" t="n"/>
       <c r="AE91" s="24" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
+      <c r="AF91" s="11" t="n"/>
+      <c r="AG91" s="11" t="n"/>
+      <c r="AH91" s="11" t="n"/>
       <c r="AI91" s="25" t="n"/>
       <c r="AJ91" s="25" t="n"/>
       <c r="AK91" s="25" t="n"/>
@@ -2125,17 +2158,17 @@
       <c r="D92" t="n">
         <v>70</v>
       </c>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
-      <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="10" t="n"/>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="n"/>
-      <c r="O92" s="10" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="11" t="n"/>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="11" t="n"/>
+      <c r="K92" s="11" t="n"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="11" t="n"/>
+      <c r="O92" s="11" t="n"/>
       <c r="P92" s="23" t="n"/>
       <c r="Q92" s="23" t="n"/>
       <c r="R92" s="24" t="n"/>
@@ -2152,9 +2185,9 @@
       <c r="AC92" s="24" t="n"/>
       <c r="AD92" s="24" t="n"/>
       <c r="AE92" s="24" t="n"/>
-      <c r="AF92" s="10" t="n"/>
-      <c r="AG92" s="10" t="n"/>
-      <c r="AH92" s="10" t="n"/>
+      <c r="AF92" s="11" t="n"/>
+      <c r="AG92" s="11" t="n"/>
+      <c r="AH92" s="11" t="n"/>
       <c r="AI92" s="25" t="n"/>
       <c r="AJ92" s="25" t="n"/>
       <c r="AK92" s="25" t="n"/>
@@ -2176,17 +2209,17 @@
       <c r="D93" t="n">
         <v>60</v>
       </c>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="11" t="n"/>
+      <c r="I93" s="11" t="n"/>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="11" t="n"/>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="11" t="n"/>
+      <c r="O93" s="11" t="n"/>
       <c r="P93" s="23" t="n"/>
       <c r="Q93" s="23" t="n"/>
       <c r="R93" s="24" t="n"/>
@@ -2203,9 +2236,9 @@
       <c r="AC93" s="24" t="n"/>
       <c r="AD93" s="24" t="n"/>
       <c r="AE93" s="24" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
+      <c r="AF93" s="11" t="n"/>
+      <c r="AG93" s="11" t="n"/>
+      <c r="AH93" s="11" t="n"/>
       <c r="AI93" s="25" t="n"/>
       <c r="AJ93" s="25" t="n"/>
       <c r="AK93" s="25" t="n"/>
@@ -2227,17 +2260,17 @@
       <c r="D94" t="n">
         <v>50</v>
       </c>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="11" t="n"/>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="11" t="n"/>
+      <c r="K94" s="11" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="11" t="n"/>
+      <c r="O94" s="11" t="n"/>
       <c r="P94" s="23" t="n"/>
       <c r="Q94" s="23" t="n"/>
       <c r="R94" s="24" t="n"/>
@@ -2254,9 +2287,9 @@
       <c r="AC94" s="24" t="n"/>
       <c r="AD94" s="24" t="n"/>
       <c r="AE94" s="24" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
+      <c r="AF94" s="11" t="n"/>
+      <c r="AG94" s="11" t="n"/>
+      <c r="AH94" s="11" t="n"/>
       <c r="AI94" s="25" t="n"/>
       <c r="AJ94" s="25" t="n"/>
       <c r="AK94" s="25" t="n"/>
@@ -2278,17 +2311,17 @@
       <c r="D95" t="n">
         <v>40</v>
       </c>
-      <c r="E95" s="10" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="10" t="n"/>
-      <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="n"/>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="10" t="n"/>
-      <c r="M95" s="10" t="n"/>
-      <c r="N95" s="10" t="n"/>
-      <c r="O95" s="10" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="11" t="n"/>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="11" t="n"/>
+      <c r="O95" s="11" t="n"/>
       <c r="P95" s="23" t="n"/>
       <c r="Q95" s="23" t="n"/>
       <c r="R95" s="24" t="n"/>
@@ -2305,9 +2338,9 @@
       <c r="AC95" s="24" t="n"/>
       <c r="AD95" s="24" t="n"/>
       <c r="AE95" s="24" t="n"/>
-      <c r="AF95" s="10" t="n"/>
-      <c r="AG95" s="10" t="n"/>
-      <c r="AH95" s="10" t="n"/>
+      <c r="AF95" s="11" t="n"/>
+      <c r="AG95" s="11" t="n"/>
+      <c r="AH95" s="11" t="n"/>
       <c r="AI95" s="25" t="n"/>
       <c r="AJ95" s="25" t="n"/>
       <c r="AK95" s="25" t="n"/>
@@ -2329,17 +2362,17 @@
       <c r="D96" t="n">
         <v>30</v>
       </c>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="11" t="n"/>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="11" t="n"/>
+      <c r="K96" s="11" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="11" t="n"/>
+      <c r="N96" s="11" t="n"/>
+      <c r="O96" s="11" t="n"/>
       <c r="P96" s="23" t="n"/>
       <c r="Q96" s="23" t="n"/>
       <c r="R96" s="24" t="n"/>
@@ -2356,9 +2389,9 @@
       <c r="AC96" s="24" t="n"/>
       <c r="AD96" s="24" t="n"/>
       <c r="AE96" s="24" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
+      <c r="AF96" s="11" t="n"/>
+      <c r="AG96" s="11" t="n"/>
+      <c r="AH96" s="11" t="n"/>
       <c r="AI96" s="25" t="n"/>
       <c r="AJ96" s="25" t="n"/>
       <c r="AK96" s="25" t="n"/>
@@ -2380,17 +2413,17 @@
       <c r="D97" t="n">
         <v>20</v>
       </c>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="11" t="n"/>
+      <c r="I97" s="11" t="n"/>
+      <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+      <c r="O97" s="11" t="n"/>
       <c r="P97" s="23" t="n"/>
       <c r="Q97" s="23" t="n"/>
       <c r="R97" s="24" t="n"/>
@@ -2407,9 +2440,9 @@
       <c r="AC97" s="24" t="n"/>
       <c r="AD97" s="24" t="n"/>
       <c r="AE97" s="24" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
+      <c r="AF97" s="11" t="n"/>
+      <c r="AG97" s="11" t="n"/>
+      <c r="AH97" s="11" t="n"/>
       <c r="AI97" s="25" t="n"/>
       <c r="AJ97" s="25" t="n"/>
       <c r="AK97" s="25" t="n"/>
@@ -2431,17 +2464,17 @@
       <c r="D98" t="n">
         <v>10</v>
       </c>
-      <c r="E98" s="10" t="n"/>
-      <c r="F98" s="10" t="n"/>
-      <c r="G98" s="10" t="n"/>
-      <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="n"/>
-      <c r="J98" s="10" t="n"/>
-      <c r="K98" s="10" t="n"/>
-      <c r="L98" s="10" t="n"/>
-      <c r="M98" s="10" t="n"/>
-      <c r="N98" s="10" t="n"/>
-      <c r="O98" s="10" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="11" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="11" t="n"/>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+      <c r="O98" s="11" t="n"/>
       <c r="P98" s="23" t="n"/>
       <c r="Q98" s="23" t="n"/>
       <c r="R98" s="24" t="n"/>
@@ -2458,9 +2491,9 @@
       <c r="AC98" s="24" t="n"/>
       <c r="AD98" s="24" t="n"/>
       <c r="AE98" s="24" t="n"/>
-      <c r="AF98" s="10" t="n"/>
-      <c r="AG98" s="10" t="n"/>
-      <c r="AH98" s="10" t="n"/>
+      <c r="AF98" s="11" t="n"/>
+      <c r="AG98" s="11" t="n"/>
+      <c r="AH98" s="11" t="n"/>
       <c r="AI98" s="25" t="n"/>
       <c r="AJ98" s="25" t="n"/>
       <c r="AK98" s="25" t="n"/>
@@ -2482,17 +2515,17 @@
       <c r="D99" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="11" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
+      <c r="O99" s="11" t="n"/>
       <c r="P99" s="23" t="n"/>
       <c r="Q99" s="23" t="n"/>
       <c r="R99" s="24" t="n"/>
@@ -2509,9 +2542,9 @@
       <c r="AC99" s="24" t="n"/>
       <c r="AD99" s="24" t="n"/>
       <c r="AE99" s="24" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
+      <c r="AF99" s="11" t="n"/>
+      <c r="AG99" s="11" t="n"/>
+      <c r="AH99" s="11" t="n"/>
       <c r="AI99" s="25" t="n"/>
       <c r="AJ99" s="25" t="n"/>
       <c r="AK99" s="25" t="n"/>
@@ -2533,17 +2566,17 @@
       <c r="D100" t="n">
         <v>90</v>
       </c>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="11" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="11" t="n"/>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="11" t="n"/>
+      <c r="O100" s="11" t="n"/>
       <c r="P100" s="23" t="n"/>
       <c r="Q100" s="23" t="n"/>
       <c r="R100" s="24" t="n"/>
@@ -2560,9 +2593,9 @@
       <c r="AC100" s="24" t="n"/>
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="24" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
+      <c r="AF100" s="11" t="n"/>
+      <c r="AG100" s="11" t="n"/>
+      <c r="AH100" s="11" t="n"/>
       <c r="AI100" s="25" t="n"/>
       <c r="AJ100" s="25" t="n"/>
       <c r="AK100" s="25" t="n"/>
@@ -2584,17 +2617,17 @@
       <c r="D101" t="n">
         <v>80</v>
       </c>
-      <c r="E101" s="10" t="n"/>
-      <c r="F101" s="10" t="n"/>
-      <c r="G101" s="10" t="n"/>
-      <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n"/>
-      <c r="M101" s="10" t="n"/>
-      <c r="N101" s="10" t="n"/>
-      <c r="O101" s="10" t="n"/>
+      <c r="E101" s="11" t="n"/>
+      <c r="F101" s="11" t="n"/>
+      <c r="G101" s="11" t="n"/>
+      <c r="H101" s="11" t="n"/>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="11" t="n"/>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="n"/>
+      <c r="O101" s="11" t="n"/>
       <c r="P101" s="23" t="n"/>
       <c r="Q101" s="23" t="n"/>
       <c r="R101" s="24" t="n"/>
@@ -2611,9 +2644,9 @@
       <c r="AC101" s="24" t="n"/>
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="24" t="n"/>
-      <c r="AF101" s="10" t="n"/>
-      <c r="AG101" s="10" t="n"/>
-      <c r="AH101" s="10" t="n"/>
+      <c r="AF101" s="11" t="n"/>
+      <c r="AG101" s="11" t="n"/>
+      <c r="AH101" s="11" t="n"/>
       <c r="AI101" s="25" t="n"/>
       <c r="AJ101" s="25" t="n"/>
       <c r="AK101" s="25" t="n"/>
@@ -2635,17 +2668,17 @@
       <c r="D102" t="n">
         <v>70</v>
       </c>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
+      <c r="E102" s="11" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="11" t="n"/>
+      <c r="H102" s="11" t="n"/>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="11" t="n"/>
+      <c r="K102" s="11" t="n"/>
+      <c r="L102" s="11" t="n"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="11" t="n"/>
+      <c r="O102" s="11" t="n"/>
       <c r="P102" s="23" t="n"/>
       <c r="Q102" s="23" t="n"/>
       <c r="R102" s="24" t="n"/>
@@ -2662,9 +2695,9 @@
       <c r="AC102" s="24" t="n"/>
       <c r="AD102" s="24" t="n"/>
       <c r="AE102" s="24" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
+      <c r="AF102" s="11" t="n"/>
+      <c r="AG102" s="11" t="n"/>
+      <c r="AH102" s="11" t="n"/>
       <c r="AI102" s="25" t="n"/>
       <c r="AJ102" s="25" t="n"/>
       <c r="AK102" s="25" t="n"/>
@@ -2686,17 +2719,17 @@
       <c r="D103" t="n">
         <v>60</v>
       </c>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
+      <c r="E103" s="11" t="n"/>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="11" t="n"/>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="11" t="n"/>
+      <c r="O103" s="11" t="n"/>
       <c r="P103" s="23" t="n"/>
       <c r="Q103" s="23" t="n"/>
       <c r="R103" s="24" t="n"/>
@@ -2713,9 +2746,9 @@
       <c r="AC103" s="24" t="n"/>
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="24" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
+      <c r="AF103" s="11" t="n"/>
+      <c r="AG103" s="11" t="n"/>
+      <c r="AH103" s="11" t="n"/>
       <c r="AI103" s="25" t="n"/>
       <c r="AJ103" s="25" t="n"/>
       <c r="AK103" s="25" t="n"/>
@@ -2737,17 +2770,17 @@
       <c r="D104" t="n">
         <v>50</v>
       </c>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
+      <c r="E104" s="11" t="n"/>
+      <c r="F104" s="11" t="n"/>
+      <c r="G104" s="11" t="n"/>
+      <c r="H104" s="11" t="n"/>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="11" t="n"/>
+      <c r="K104" s="11" t="n"/>
+      <c r="L104" s="11" t="n"/>
+      <c r="M104" s="11" t="n"/>
+      <c r="N104" s="11" t="n"/>
+      <c r="O104" s="11" t="n"/>
       <c r="P104" s="23" t="n"/>
       <c r="Q104" s="23" t="n"/>
       <c r="R104" s="24" t="n"/>
@@ -2764,9 +2797,9 @@
       <c r="AC104" s="24" t="n"/>
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="24" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
+      <c r="AF104" s="11" t="n"/>
+      <c r="AG104" s="11" t="n"/>
+      <c r="AH104" s="11" t="n"/>
       <c r="AI104" s="25" t="n"/>
       <c r="AJ104" s="25" t="n"/>
       <c r="AK104" s="25" t="n"/>
@@ -2788,17 +2821,17 @@
       <c r="D105" t="n">
         <v>40</v>
       </c>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
+      <c r="E105" s="11" t="n"/>
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="11" t="n"/>
+      <c r="H105" s="11" t="n"/>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="11" t="n"/>
+      <c r="K105" s="11" t="n"/>
+      <c r="L105" s="11" t="n"/>
+      <c r="M105" s="11" t="n"/>
+      <c r="N105" s="11" t="n"/>
+      <c r="O105" s="11" t="n"/>
       <c r="P105" s="23" t="n"/>
       <c r="Q105" s="23" t="n"/>
       <c r="R105" s="24" t="n"/>
@@ -2815,9 +2848,9 @@
       <c r="AC105" s="24" t="n"/>
       <c r="AD105" s="24" t="n"/>
       <c r="AE105" s="24" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
+      <c r="AF105" s="11" t="n"/>
+      <c r="AG105" s="11" t="n"/>
+      <c r="AH105" s="11" t="n"/>
       <c r="AI105" s="25" t="n"/>
       <c r="AJ105" s="25" t="n"/>
       <c r="AK105" s="25" t="n"/>
@@ -2839,17 +2872,17 @@
       <c r="D106" t="n">
         <v>30</v>
       </c>
-      <c r="E106" s="10" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="10" t="n"/>
-      <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
-      <c r="J106" s="10" t="n"/>
-      <c r="K106" s="10" t="n"/>
-      <c r="L106" s="10" t="n"/>
-      <c r="M106" s="10" t="n"/>
-      <c r="N106" s="10" t="n"/>
-      <c r="O106" s="10" t="n"/>
+      <c r="E106" s="11" t="n"/>
+      <c r="F106" s="11" t="n"/>
+      <c r="G106" s="11" t="n"/>
+      <c r="H106" s="11" t="n"/>
+      <c r="I106" s="11" t="n"/>
+      <c r="J106" s="11" t="n"/>
+      <c r="K106" s="11" t="n"/>
+      <c r="L106" s="11" t="n"/>
+      <c r="M106" s="11" t="n"/>
+      <c r="N106" s="11" t="n"/>
+      <c r="O106" s="11" t="n"/>
       <c r="P106" s="23" t="n"/>
       <c r="Q106" s="23" t="n"/>
       <c r="R106" s="24" t="n"/>
@@ -2866,9 +2899,9 @@
       <c r="AC106" s="24" t="n"/>
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="24" t="n"/>
-      <c r="AF106" s="10" t="n"/>
-      <c r="AG106" s="10" t="n"/>
-      <c r="AH106" s="10" t="n"/>
+      <c r="AF106" s="11" t="n"/>
+      <c r="AG106" s="11" t="n"/>
+      <c r="AH106" s="11" t="n"/>
       <c r="AI106" s="25" t="n"/>
       <c r="AJ106" s="25" t="n"/>
       <c r="AK106" s="25" t="n"/>
@@ -2890,17 +2923,17 @@
       <c r="D107" t="n">
         <v>20</v>
       </c>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="10" t="n"/>
-      <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
-      <c r="L107" s="10" t="n"/>
-      <c r="M107" s="10" t="n"/>
-      <c r="N107" s="10" t="n"/>
-      <c r="O107" s="10" t="n"/>
+      <c r="E107" s="11" t="n"/>
+      <c r="F107" s="11" t="n"/>
+      <c r="G107" s="11" t="n"/>
+      <c r="H107" s="11" t="n"/>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="11" t="n"/>
+      <c r="K107" s="11" t="n"/>
+      <c r="L107" s="11" t="n"/>
+      <c r="M107" s="11" t="n"/>
+      <c r="N107" s="11" t="n"/>
+      <c r="O107" s="11" t="n"/>
       <c r="P107" s="23" t="n"/>
       <c r="Q107" s="23" t="n"/>
       <c r="R107" s="24" t="n"/>
@@ -2917,9 +2950,9 @@
       <c r="AC107" s="24" t="n"/>
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="24" t="n"/>
-      <c r="AF107" s="10" t="n"/>
-      <c r="AG107" s="10" t="n"/>
-      <c r="AH107" s="10" t="n"/>
+      <c r="AF107" s="11" t="n"/>
+      <c r="AG107" s="11" t="n"/>
+      <c r="AH107" s="11" t="n"/>
       <c r="AI107" s="25" t="n"/>
       <c r="AJ107" s="25" t="n"/>
       <c r="AK107" s="25" t="n"/>
@@ -2941,17 +2974,17 @@
       <c r="D108" t="n">
         <v>10</v>
       </c>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
+      <c r="E108" s="11" t="n"/>
+      <c r="F108" s="11" t="n"/>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="11" t="n"/>
+      <c r="I108" s="11" t="n"/>
+      <c r="J108" s="11" t="n"/>
+      <c r="K108" s="11" t="n"/>
+      <c r="L108" s="11" t="n"/>
+      <c r="M108" s="11" t="n"/>
+      <c r="N108" s="11" t="n"/>
+      <c r="O108" s="11" t="n"/>
       <c r="P108" s="23" t="n"/>
       <c r="Q108" s="23" t="n"/>
       <c r="R108" s="24" t="n"/>
@@ -2968,9 +3001,9 @@
       <c r="AC108" s="24" t="n"/>
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="24" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
+      <c r="AF108" s="11" t="n"/>
+      <c r="AG108" s="11" t="n"/>
+      <c r="AH108" s="11" t="n"/>
       <c r="AI108" s="25" t="n"/>
       <c r="AJ108" s="25" t="n"/>
       <c r="AK108" s="25" t="n"/>
@@ -2992,17 +3025,17 @@
       <c r="D109" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="10" t="n"/>
-      <c r="F109" s="10" t="n"/>
-      <c r="G109" s="10" t="n"/>
-      <c r="H109" s="10" t="n"/>
-      <c r="I109" s="10" t="n"/>
-      <c r="J109" s="10" t="n"/>
-      <c r="K109" s="10" t="n"/>
-      <c r="L109" s="10" t="n"/>
-      <c r="M109" s="10" t="n"/>
-      <c r="N109" s="10" t="n"/>
-      <c r="O109" s="10" t="n"/>
+      <c r="E109" s="11" t="n"/>
+      <c r="F109" s="11" t="n"/>
+      <c r="G109" s="11" t="n"/>
+      <c r="H109" s="11" t="n"/>
+      <c r="I109" s="11" t="n"/>
+      <c r="J109" s="11" t="n"/>
+      <c r="K109" s="11" t="n"/>
+      <c r="L109" s="11" t="n"/>
+      <c r="M109" s="11" t="n"/>
+      <c r="N109" s="11" t="n"/>
+      <c r="O109" s="11" t="n"/>
       <c r="P109" s="23" t="n"/>
       <c r="Q109" s="23" t="n"/>
       <c r="R109" s="24" t="n"/>
@@ -3019,9 +3052,9 @@
       <c r="AC109" s="24" t="n"/>
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="24" t="n"/>
-      <c r="AF109" s="10" t="n"/>
-      <c r="AG109" s="10" t="n"/>
-      <c r="AH109" s="10" t="n"/>
+      <c r="AF109" s="11" t="n"/>
+      <c r="AG109" s="11" t="n"/>
+      <c r="AH109" s="11" t="n"/>
       <c r="AI109" s="25" t="n"/>
       <c r="AJ109" s="25" t="n"/>
       <c r="AK109" s="25" t="n"/>
@@ -3043,17 +3076,17 @@
       <c r="D110" t="n">
         <v>80</v>
       </c>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="11" t="n"/>
+      <c r="G110" s="11" t="n"/>
+      <c r="H110" s="11" t="n"/>
+      <c r="I110" s="11" t="n"/>
+      <c r="J110" s="11" t="n"/>
+      <c r="K110" s="11" t="n"/>
+      <c r="L110" s="11" t="n"/>
+      <c r="M110" s="11" t="n"/>
+      <c r="N110" s="11" t="n"/>
+      <c r="O110" s="11" t="n"/>
       <c r="P110" s="23" t="n"/>
       <c r="Q110" s="23" t="n"/>
       <c r="R110" s="24" t="n"/>
@@ -3070,9 +3103,9 @@
       <c r="AC110" s="24" t="n"/>
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="24" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
+      <c r="AF110" s="11" t="n"/>
+      <c r="AG110" s="11" t="n"/>
+      <c r="AH110" s="11" t="n"/>
       <c r="AI110" s="25" t="n"/>
       <c r="AJ110" s="25" t="n"/>
       <c r="AK110" s="25" t="n"/>
@@ -3094,17 +3127,17 @@
       <c r="D111" t="n">
         <v>70</v>
       </c>
-      <c r="E111" s="10" t="n"/>
-      <c r="F111" s="10" t="n"/>
-      <c r="G111" s="10" t="n"/>
-      <c r="H111" s="10" t="n"/>
-      <c r="I111" s="10" t="n"/>
-      <c r="J111" s="10" t="n"/>
-      <c r="K111" s="10" t="n"/>
-      <c r="L111" s="10" t="n"/>
-      <c r="M111" s="10" t="n"/>
-      <c r="N111" s="10" t="n"/>
-      <c r="O111" s="10" t="n"/>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="11" t="n"/>
+      <c r="G111" s="11" t="n"/>
+      <c r="H111" s="11" t="n"/>
+      <c r="I111" s="11" t="n"/>
+      <c r="J111" s="11" t="n"/>
+      <c r="K111" s="11" t="n"/>
+      <c r="L111" s="11" t="n"/>
+      <c r="M111" s="11" t="n"/>
+      <c r="N111" s="11" t="n"/>
+      <c r="O111" s="11" t="n"/>
       <c r="P111" s="23" t="n"/>
       <c r="Q111" s="23" t="n"/>
       <c r="R111" s="24" t="n"/>
@@ -3121,9 +3154,9 @@
       <c r="AC111" s="24" t="n"/>
       <c r="AD111" s="24" t="n"/>
       <c r="AE111" s="24" t="n"/>
-      <c r="AF111" s="10" t="n"/>
-      <c r="AG111" s="10" t="n"/>
-      <c r="AH111" s="10" t="n"/>
+      <c r="AF111" s="11" t="n"/>
+      <c r="AG111" s="11" t="n"/>
+      <c r="AH111" s="11" t="n"/>
       <c r="AI111" s="25" t="n"/>
       <c r="AJ111" s="25" t="n"/>
       <c r="AK111" s="25" t="n"/>
@@ -3145,17 +3178,17 @@
       <c r="D112" t="n">
         <v>60</v>
       </c>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="11" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+      <c r="O112" s="11" t="n"/>
       <c r="P112" s="23" t="n"/>
       <c r="Q112" s="23" t="n"/>
       <c r="R112" s="24" t="n"/>
@@ -3172,9 +3205,9 @@
       <c r="AC112" s="24" t="n"/>
       <c r="AD112" s="24" t="n"/>
       <c r="AE112" s="24" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
+      <c r="AF112" s="11" t="n"/>
+      <c r="AG112" s="11" t="n"/>
+      <c r="AH112" s="11" t="n"/>
       <c r="AI112" s="25" t="n"/>
       <c r="AJ112" s="25" t="n"/>
       <c r="AK112" s="25" t="n"/>
@@ -3196,17 +3229,17 @@
       <c r="D113" t="n">
         <v>50</v>
       </c>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
+      <c r="E113" s="11" t="n"/>
+      <c r="F113" s="11" t="n"/>
+      <c r="G113" s="11" t="n"/>
+      <c r="H113" s="11" t="n"/>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="11" t="n"/>
+      <c r="K113" s="11" t="n"/>
+      <c r="L113" s="11" t="n"/>
+      <c r="M113" s="11" t="n"/>
+      <c r="N113" s="11" t="n"/>
+      <c r="O113" s="11" t="n"/>
       <c r="P113" s="23" t="n"/>
       <c r="Q113" s="23" t="n"/>
       <c r="R113" s="24" t="n"/>
@@ -3223,9 +3256,9 @@
       <c r="AC113" s="24" t="n"/>
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="24" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
+      <c r="AF113" s="11" t="n"/>
+      <c r="AG113" s="11" t="n"/>
+      <c r="AH113" s="11" t="n"/>
       <c r="AI113" s="25" t="n"/>
       <c r="AJ113" s="25" t="n"/>
       <c r="AK113" s="25" t="n"/>
@@ -3247,17 +3280,17 @@
       <c r="D114" t="n">
         <v>40</v>
       </c>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="n"/>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="n"/>
-      <c r="O114" s="10" t="n"/>
+      <c r="E114" s="11" t="n"/>
+      <c r="F114" s="11" t="n"/>
+      <c r="G114" s="11" t="n"/>
+      <c r="H114" s="11" t="n"/>
+      <c r="I114" s="11" t="n"/>
+      <c r="J114" s="11" t="n"/>
+      <c r="K114" s="11" t="n"/>
+      <c r="L114" s="11" t="n"/>
+      <c r="M114" s="11" t="n"/>
+      <c r="N114" s="11" t="n"/>
+      <c r="O114" s="11" t="n"/>
       <c r="P114" s="23" t="n"/>
       <c r="Q114" s="23" t="n"/>
       <c r="R114" s="24" t="n"/>
@@ -3274,9 +3307,9 @@
       <c r="AC114" s="24" t="n"/>
       <c r="AD114" s="24" t="n"/>
       <c r="AE114" s="24" t="n"/>
-      <c r="AF114" s="10" t="n"/>
-      <c r="AG114" s="10" t="n"/>
-      <c r="AH114" s="10" t="n"/>
+      <c r="AF114" s="11" t="n"/>
+      <c r="AG114" s="11" t="n"/>
+      <c r="AH114" s="11" t="n"/>
       <c r="AI114" s="25" t="n"/>
       <c r="AJ114" s="25" t="n"/>
       <c r="AK114" s="25" t="n"/>
@@ -3298,17 +3331,17 @@
       <c r="D115" t="n">
         <v>30</v>
       </c>
-      <c r="E115" s="10" t="n"/>
-      <c r="F115" s="10" t="n"/>
-      <c r="G115" s="10" t="n"/>
-      <c r="H115" s="10" t="n"/>
-      <c r="I115" s="10" t="n"/>
-      <c r="J115" s="10" t="n"/>
-      <c r="K115" s="10" t="n"/>
-      <c r="L115" s="10" t="n"/>
-      <c r="M115" s="10" t="n"/>
-      <c r="N115" s="10" t="n"/>
-      <c r="O115" s="10" t="n"/>
+      <c r="E115" s="11" t="n"/>
+      <c r="F115" s="11" t="n"/>
+      <c r="G115" s="11" t="n"/>
+      <c r="H115" s="11" t="n"/>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="11" t="n"/>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="11" t="n"/>
+      <c r="O115" s="11" t="n"/>
       <c r="P115" s="23" t="n"/>
       <c r="Q115" s="23" t="n"/>
       <c r="R115" s="24" t="n"/>
@@ -3325,9 +3358,9 @@
       <c r="AC115" s="24" t="n"/>
       <c r="AD115" s="24" t="n"/>
       <c r="AE115" s="24" t="n"/>
-      <c r="AF115" s="10" t="n"/>
-      <c r="AG115" s="10" t="n"/>
-      <c r="AH115" s="10" t="n"/>
+      <c r="AF115" s="11" t="n"/>
+      <c r="AG115" s="11" t="n"/>
+      <c r="AH115" s="11" t="n"/>
       <c r="AI115" s="25" t="n"/>
       <c r="AJ115" s="25" t="n"/>
       <c r="AK115" s="25" t="n"/>
@@ -3349,17 +3382,17 @@
       <c r="D116" t="n">
         <v>20</v>
       </c>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="11" t="n"/>
+      <c r="K116" s="11" t="n"/>
+      <c r="L116" s="11" t="n"/>
+      <c r="M116" s="11" t="n"/>
+      <c r="N116" s="11" t="n"/>
+      <c r="O116" s="11" t="n"/>
       <c r="P116" s="23" t="n"/>
       <c r="Q116" s="23" t="n"/>
       <c r="R116" s="24" t="n"/>
@@ -3376,9 +3409,9 @@
       <c r="AC116" s="24" t="n"/>
       <c r="AD116" s="24" t="n"/>
       <c r="AE116" s="24" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
+      <c r="AF116" s="11" t="n"/>
+      <c r="AG116" s="11" t="n"/>
+      <c r="AH116" s="11" t="n"/>
       <c r="AI116" s="25" t="n"/>
       <c r="AJ116" s="25" t="n"/>
       <c r="AK116" s="25" t="n"/>
@@ -3400,17 +3433,17 @@
       <c r="D117" t="n">
         <v>10</v>
       </c>
-      <c r="E117" s="10" t="n"/>
-      <c r="F117" s="10" t="n"/>
-      <c r="G117" s="10" t="n"/>
-      <c r="H117" s="10" t="n"/>
-      <c r="I117" s="10" t="n"/>
-      <c r="J117" s="10" t="n"/>
-      <c r="K117" s="10" t="n"/>
-      <c r="L117" s="10" t="n"/>
-      <c r="M117" s="10" t="n"/>
-      <c r="N117" s="10" t="n"/>
-      <c r="O117" s="10" t="n"/>
+      <c r="E117" s="11" t="n"/>
+      <c r="F117" s="11" t="n"/>
+      <c r="G117" s="11" t="n"/>
+      <c r="H117" s="11" t="n"/>
+      <c r="I117" s="11" t="n"/>
+      <c r="J117" s="11" t="n"/>
+      <c r="K117" s="11" t="n"/>
+      <c r="L117" s="11" t="n"/>
+      <c r="M117" s="11" t="n"/>
+      <c r="N117" s="11" t="n"/>
+      <c r="O117" s="11" t="n"/>
       <c r="P117" s="23" t="n"/>
       <c r="Q117" s="23" t="n"/>
       <c r="R117" s="24" t="n"/>
@@ -3427,9 +3460,9 @@
       <c r="AC117" s="24" t="n"/>
       <c r="AD117" s="24" t="n"/>
       <c r="AE117" s="24" t="n"/>
-      <c r="AF117" s="10" t="n"/>
-      <c r="AG117" s="10" t="n"/>
-      <c r="AH117" s="10" t="n"/>
+      <c r="AF117" s="11" t="n"/>
+      <c r="AG117" s="11" t="n"/>
+      <c r="AH117" s="11" t="n"/>
       <c r="AI117" s="25" t="n"/>
       <c r="AJ117" s="25" t="n"/>
       <c r="AK117" s="25" t="n"/>
@@ -3451,17 +3484,17 @@
       <c r="D118" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="10" t="n"/>
-      <c r="F118" s="10" t="n"/>
-      <c r="G118" s="10" t="n"/>
-      <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="n"/>
-      <c r="J118" s="10" t="n"/>
-      <c r="K118" s="10" t="n"/>
-      <c r="L118" s="10" t="n"/>
-      <c r="M118" s="10" t="n"/>
-      <c r="N118" s="10" t="n"/>
-      <c r="O118" s="10" t="n"/>
+      <c r="E118" s="11" t="n"/>
+      <c r="F118" s="11" t="n"/>
+      <c r="G118" s="11" t="n"/>
+      <c r="H118" s="11" t="n"/>
+      <c r="I118" s="11" t="n"/>
+      <c r="J118" s="11" t="n"/>
+      <c r="K118" s="11" t="n"/>
+      <c r="L118" s="11" t="n"/>
+      <c r="M118" s="11" t="n"/>
+      <c r="N118" s="11" t="n"/>
+      <c r="O118" s="11" t="n"/>
       <c r="P118" s="23" t="n"/>
       <c r="Q118" s="23" t="n"/>
       <c r="R118" s="24" t="n"/>
@@ -3478,9 +3511,9 @@
       <c r="AC118" s="24" t="n"/>
       <c r="AD118" s="24" t="n"/>
       <c r="AE118" s="24" t="n"/>
-      <c r="AF118" s="10" t="n"/>
-      <c r="AG118" s="10" t="n"/>
-      <c r="AH118" s="10" t="n"/>
+      <c r="AF118" s="11" t="n"/>
+      <c r="AG118" s="11" t="n"/>
+      <c r="AH118" s="11" t="n"/>
       <c r="AI118" s="25" t="n"/>
       <c r="AJ118" s="25" t="n"/>
       <c r="AK118" s="25" t="n"/>
@@ -3502,17 +3535,17 @@
       <c r="D119" t="n">
         <v>70</v>
       </c>
-      <c r="E119" s="10" t="n"/>
-      <c r="F119" s="10" t="n"/>
-      <c r="G119" s="10" t="n"/>
-      <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="10" t="n"/>
-      <c r="K119" s="10" t="n"/>
-      <c r="L119" s="10" t="n"/>
-      <c r="M119" s="10" t="n"/>
-      <c r="N119" s="10" t="n"/>
-      <c r="O119" s="10" t="n"/>
+      <c r="E119" s="11" t="n"/>
+      <c r="F119" s="11" t="n"/>
+      <c r="G119" s="11" t="n"/>
+      <c r="H119" s="11" t="n"/>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="11" t="n"/>
+      <c r="K119" s="11" t="n"/>
+      <c r="L119" s="11" t="n"/>
+      <c r="M119" s="11" t="n"/>
+      <c r="N119" s="11" t="n"/>
+      <c r="O119" s="11" t="n"/>
       <c r="P119" s="23" t="n"/>
       <c r="Q119" s="23" t="n"/>
       <c r="R119" s="24" t="n"/>
@@ -3529,9 +3562,9 @@
       <c r="AC119" s="24" t="n"/>
       <c r="AD119" s="24" t="n"/>
       <c r="AE119" s="24" t="n"/>
-      <c r="AF119" s="10" t="n"/>
-      <c r="AG119" s="10" t="n"/>
-      <c r="AH119" s="10" t="n"/>
+      <c r="AF119" s="11" t="n"/>
+      <c r="AG119" s="11" t="n"/>
+      <c r="AH119" s="11" t="n"/>
       <c r="AI119" s="25" t="n"/>
       <c r="AJ119" s="25" t="n"/>
       <c r="AK119" s="25" t="n"/>
@@ -3553,17 +3586,17 @@
       <c r="D120" t="n">
         <v>60</v>
       </c>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="10" t="n"/>
-      <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="n"/>
-      <c r="M120" s="10" t="n"/>
-      <c r="N120" s="10" t="n"/>
-      <c r="O120" s="10" t="n"/>
+      <c r="E120" s="11" t="n"/>
+      <c r="F120" s="11" t="n"/>
+      <c r="G120" s="11" t="n"/>
+      <c r="H120" s="11" t="n"/>
+      <c r="I120" s="11" t="n"/>
+      <c r="J120" s="11" t="n"/>
+      <c r="K120" s="11" t="n"/>
+      <c r="L120" s="11" t="n"/>
+      <c r="M120" s="11" t="n"/>
+      <c r="N120" s="11" t="n"/>
+      <c r="O120" s="11" t="n"/>
       <c r="P120" s="23" t="n"/>
       <c r="Q120" s="23" t="n"/>
       <c r="R120" s="24" t="n"/>
@@ -3580,9 +3613,9 @@
       <c r="AC120" s="24" t="n"/>
       <c r="AD120" s="24" t="n"/>
       <c r="AE120" s="24" t="n"/>
-      <c r="AF120" s="10" t="n"/>
-      <c r="AG120" s="10" t="n"/>
-      <c r="AH120" s="10" t="n"/>
+      <c r="AF120" s="11" t="n"/>
+      <c r="AG120" s="11" t="n"/>
+      <c r="AH120" s="11" t="n"/>
       <c r="AI120" s="25" t="n"/>
       <c r="AJ120" s="25" t="n"/>
       <c r="AK120" s="25" t="n"/>
@@ -3604,17 +3637,17 @@
       <c r="D121" t="n">
         <v>50</v>
       </c>
-      <c r="E121" s="10" t="n"/>
-      <c r="F121" s="10" t="n"/>
-      <c r="G121" s="10" t="n"/>
-      <c r="H121" s="10" t="n"/>
-      <c r="I121" s="10" t="n"/>
-      <c r="J121" s="10" t="n"/>
-      <c r="K121" s="10" t="n"/>
-      <c r="L121" s="10" t="n"/>
-      <c r="M121" s="10" t="n"/>
-      <c r="N121" s="10" t="n"/>
-      <c r="O121" s="10" t="n"/>
+      <c r="E121" s="11" t="n"/>
+      <c r="F121" s="11" t="n"/>
+      <c r="G121" s="11" t="n"/>
+      <c r="H121" s="11" t="n"/>
+      <c r="I121" s="11" t="n"/>
+      <c r="J121" s="11" t="n"/>
+      <c r="K121" s="11" t="n"/>
+      <c r="L121" s="11" t="n"/>
+      <c r="M121" s="11" t="n"/>
+      <c r="N121" s="11" t="n"/>
+      <c r="O121" s="11" t="n"/>
       <c r="P121" s="23" t="n"/>
       <c r="Q121" s="23" t="n"/>
       <c r="R121" s="24" t="n"/>
@@ -3631,9 +3664,9 @@
       <c r="AC121" s="24" t="n"/>
       <c r="AD121" s="24" t="n"/>
       <c r="AE121" s="24" t="n"/>
-      <c r="AF121" s="10" t="n"/>
-      <c r="AG121" s="10" t="n"/>
-      <c r="AH121" s="10" t="n"/>
+      <c r="AF121" s="11" t="n"/>
+      <c r="AG121" s="11" t="n"/>
+      <c r="AH121" s="11" t="n"/>
       <c r="AI121" s="25" t="n"/>
       <c r="AJ121" s="25" t="n"/>
       <c r="AK121" s="25" t="n"/>
@@ -3655,17 +3688,17 @@
       <c r="D122" t="n">
         <v>40</v>
       </c>
-      <c r="E122" s="10" t="n"/>
-      <c r="F122" s="10" t="n"/>
-      <c r="G122" s="10" t="n"/>
-      <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="n"/>
-      <c r="J122" s="10" t="n"/>
-      <c r="K122" s="10" t="n"/>
-      <c r="L122" s="10" t="n"/>
-      <c r="M122" s="10" t="n"/>
-      <c r="N122" s="10" t="n"/>
-      <c r="O122" s="10" t="n"/>
+      <c r="E122" s="11" t="n"/>
+      <c r="F122" s="11" t="n"/>
+      <c r="G122" s="11" t="n"/>
+      <c r="H122" s="11" t="n"/>
+      <c r="I122" s="11" t="n"/>
+      <c r="J122" s="11" t="n"/>
+      <c r="K122" s="11" t="n"/>
+      <c r="L122" s="11" t="n"/>
+      <c r="M122" s="11" t="n"/>
+      <c r="N122" s="11" t="n"/>
+      <c r="O122" s="11" t="n"/>
       <c r="P122" s="23" t="n"/>
       <c r="Q122" s="23" t="n"/>
       <c r="R122" s="24" t="n"/>
@@ -3682,9 +3715,9 @@
       <c r="AC122" s="24" t="n"/>
       <c r="AD122" s="24" t="n"/>
       <c r="AE122" s="24" t="n"/>
-      <c r="AF122" s="10" t="n"/>
-      <c r="AG122" s="10" t="n"/>
-      <c r="AH122" s="10" t="n"/>
+      <c r="AF122" s="11" t="n"/>
+      <c r="AG122" s="11" t="n"/>
+      <c r="AH122" s="11" t="n"/>
       <c r="AI122" s="25" t="n"/>
       <c r="AJ122" s="25" t="n"/>
       <c r="AK122" s="25" t="n"/>
@@ -3706,17 +3739,17 @@
       <c r="D123" t="n">
         <v>30</v>
       </c>
-      <c r="E123" s="10" t="n"/>
-      <c r="F123" s="10" t="n"/>
-      <c r="G123" s="10" t="n"/>
-      <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="n"/>
-      <c r="J123" s="10" t="n"/>
-      <c r="K123" s="10" t="n"/>
-      <c r="L123" s="10" t="n"/>
-      <c r="M123" s="10" t="n"/>
-      <c r="N123" s="10" t="n"/>
-      <c r="O123" s="10" t="n"/>
+      <c r="E123" s="11" t="n"/>
+      <c r="F123" s="11" t="n"/>
+      <c r="G123" s="11" t="n"/>
+      <c r="H123" s="11" t="n"/>
+      <c r="I123" s="11" t="n"/>
+      <c r="J123" s="11" t="n"/>
+      <c r="K123" s="11" t="n"/>
+      <c r="L123" s="11" t="n"/>
+      <c r="M123" s="11" t="n"/>
+      <c r="N123" s="11" t="n"/>
+      <c r="O123" s="11" t="n"/>
       <c r="P123" s="23" t="n"/>
       <c r="Q123" s="23" t="n"/>
       <c r="R123" s="24" t="n"/>
@@ -3733,9 +3766,9 @@
       <c r="AC123" s="24" t="n"/>
       <c r="AD123" s="24" t="n"/>
       <c r="AE123" s="24" t="n"/>
-      <c r="AF123" s="10" t="n"/>
-      <c r="AG123" s="10" t="n"/>
-      <c r="AH123" s="10" t="n"/>
+      <c r="AF123" s="11" t="n"/>
+      <c r="AG123" s="11" t="n"/>
+      <c r="AH123" s="11" t="n"/>
       <c r="AI123" s="25" t="n"/>
       <c r="AJ123" s="25" t="n"/>
       <c r="AK123" s="25" t="n"/>
@@ -3757,17 +3790,17 @@
       <c r="D124" t="n">
         <v>20</v>
       </c>
-      <c r="E124" s="10" t="n"/>
-      <c r="F124" s="10" t="n"/>
-      <c r="G124" s="10" t="n"/>
-      <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="n"/>
-      <c r="J124" s="10" t="n"/>
-      <c r="K124" s="10" t="n"/>
-      <c r="L124" s="10" t="n"/>
-      <c r="M124" s="10" t="n"/>
-      <c r="N124" s="10" t="n"/>
-      <c r="O124" s="10" t="n"/>
+      <c r="E124" s="11" t="n"/>
+      <c r="F124" s="11" t="n"/>
+      <c r="G124" s="11" t="n"/>
+      <c r="H124" s="11" t="n"/>
+      <c r="I124" s="11" t="n"/>
+      <c r="J124" s="11" t="n"/>
+      <c r="K124" s="11" t="n"/>
+      <c r="L124" s="11" t="n"/>
+      <c r="M124" s="11" t="n"/>
+      <c r="N124" s="11" t="n"/>
+      <c r="O124" s="11" t="n"/>
       <c r="P124" s="23" t="n"/>
       <c r="Q124" s="23" t="n"/>
       <c r="R124" s="24" t="n"/>
@@ -3784,9 +3817,9 @@
       <c r="AC124" s="24" t="n"/>
       <c r="AD124" s="24" t="n"/>
       <c r="AE124" s="24" t="n"/>
-      <c r="AF124" s="10" t="n"/>
-      <c r="AG124" s="10" t="n"/>
-      <c r="AH124" s="10" t="n"/>
+      <c r="AF124" s="11" t="n"/>
+      <c r="AG124" s="11" t="n"/>
+      <c r="AH124" s="11" t="n"/>
       <c r="AI124" s="25" t="n"/>
       <c r="AJ124" s="25" t="n"/>
       <c r="AK124" s="25" t="n"/>
@@ -3808,17 +3841,17 @@
       <c r="D125" t="n">
         <v>10</v>
       </c>
-      <c r="E125" s="10" t="n"/>
-      <c r="F125" s="10" t="n"/>
-      <c r="G125" s="10" t="n"/>
-      <c r="H125" s="10" t="n"/>
-      <c r="I125" s="10" t="n"/>
-      <c r="J125" s="10" t="n"/>
-      <c r="K125" s="10" t="n"/>
-      <c r="L125" s="10" t="n"/>
-      <c r="M125" s="10" t="n"/>
-      <c r="N125" s="10" t="n"/>
-      <c r="O125" s="10" t="n"/>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="11" t="n"/>
+      <c r="G125" s="11" t="n"/>
+      <c r="H125" s="11" t="n"/>
+      <c r="I125" s="11" t="n"/>
+      <c r="J125" s="11" t="n"/>
+      <c r="K125" s="11" t="n"/>
+      <c r="L125" s="11" t="n"/>
+      <c r="M125" s="11" t="n"/>
+      <c r="N125" s="11" t="n"/>
+      <c r="O125" s="11" t="n"/>
       <c r="P125" s="23" t="n"/>
       <c r="Q125" s="23" t="n"/>
       <c r="R125" s="24" t="n"/>
@@ -3835,9 +3868,9 @@
       <c r="AC125" s="24" t="n"/>
       <c r="AD125" s="24" t="n"/>
       <c r="AE125" s="24" t="n"/>
-      <c r="AF125" s="10" t="n"/>
-      <c r="AG125" s="10" t="n"/>
-      <c r="AH125" s="10" t="n"/>
+      <c r="AF125" s="11" t="n"/>
+      <c r="AG125" s="11" t="n"/>
+      <c r="AH125" s="11" t="n"/>
       <c r="AI125" s="25" t="n"/>
       <c r="AJ125" s="25" t="n"/>
       <c r="AK125" s="25" t="n"/>
@@ -3859,17 +3892,17 @@
       <c r="D126" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="10" t="n"/>
-      <c r="F126" s="10" t="n"/>
-      <c r="G126" s="10" t="n"/>
-      <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="n"/>
-      <c r="J126" s="10" t="n"/>
-      <c r="K126" s="10" t="n"/>
-      <c r="L126" s="10" t="n"/>
-      <c r="M126" s="10" t="n"/>
-      <c r="N126" s="10" t="n"/>
-      <c r="O126" s="10" t="n"/>
+      <c r="E126" s="11" t="n"/>
+      <c r="F126" s="11" t="n"/>
+      <c r="G126" s="11" t="n"/>
+      <c r="H126" s="11" t="n"/>
+      <c r="I126" s="11" t="n"/>
+      <c r="J126" s="11" t="n"/>
+      <c r="K126" s="11" t="n"/>
+      <c r="L126" s="11" t="n"/>
+      <c r="M126" s="11" t="n"/>
+      <c r="N126" s="11" t="n"/>
+      <c r="O126" s="11" t="n"/>
       <c r="P126" s="23" t="n"/>
       <c r="Q126" s="23" t="n"/>
       <c r="R126" s="24" t="n"/>
@@ -3886,9 +3919,9 @@
       <c r="AC126" s="24" t="n"/>
       <c r="AD126" s="24" t="n"/>
       <c r="AE126" s="24" t="n"/>
-      <c r="AF126" s="10" t="n"/>
-      <c r="AG126" s="10" t="n"/>
-      <c r="AH126" s="10" t="n"/>
+      <c r="AF126" s="11" t="n"/>
+      <c r="AG126" s="11" t="n"/>
+      <c r="AH126" s="11" t="n"/>
       <c r="AI126" s="25" t="n"/>
       <c r="AJ126" s="25" t="n"/>
       <c r="AK126" s="25" t="n"/>
@@ -3910,17 +3943,17 @@
       <c r="D127" t="n">
         <v>60</v>
       </c>
-      <c r="E127" s="10" t="n"/>
-      <c r="F127" s="10" t="n"/>
-      <c r="G127" s="10" t="n"/>
-      <c r="H127" s="10" t="n"/>
-      <c r="I127" s="10" t="n"/>
-      <c r="J127" s="10" t="n"/>
-      <c r="K127" s="10" t="n"/>
-      <c r="L127" s="10" t="n"/>
-      <c r="M127" s="10" t="n"/>
-      <c r="N127" s="10" t="n"/>
-      <c r="O127" s="10" t="n"/>
+      <c r="E127" s="11" t="n"/>
+      <c r="F127" s="11" t="n"/>
+      <c r="G127" s="11" t="n"/>
+      <c r="H127" s="11" t="n"/>
+      <c r="I127" s="11" t="n"/>
+      <c r="J127" s="11" t="n"/>
+      <c r="K127" s="11" t="n"/>
+      <c r="L127" s="11" t="n"/>
+      <c r="M127" s="11" t="n"/>
+      <c r="N127" s="11" t="n"/>
+      <c r="O127" s="11" t="n"/>
       <c r="P127" s="23" t="n"/>
       <c r="Q127" s="23" t="n"/>
       <c r="R127" s="24" t="n"/>
@@ -3937,9 +3970,9 @@
       <c r="AC127" s="24" t="n"/>
       <c r="AD127" s="24" t="n"/>
       <c r="AE127" s="24" t="n"/>
-      <c r="AF127" s="10" t="n"/>
-      <c r="AG127" s="10" t="n"/>
-      <c r="AH127" s="10" t="n"/>
+      <c r="AF127" s="11" t="n"/>
+      <c r="AG127" s="11" t="n"/>
+      <c r="AH127" s="11" t="n"/>
       <c r="AI127" s="25" t="n"/>
       <c r="AJ127" s="25" t="n"/>
       <c r="AK127" s="25" t="n"/>
@@ -3961,17 +3994,17 @@
       <c r="D128" t="n">
         <v>50</v>
       </c>
-      <c r="E128" s="10" t="n"/>
-      <c r="F128" s="10" t="n"/>
-      <c r="G128" s="10" t="n"/>
-      <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="n"/>
-      <c r="J128" s="10" t="n"/>
-      <c r="K128" s="10" t="n"/>
-      <c r="L128" s="10" t="n"/>
-      <c r="M128" s="10" t="n"/>
-      <c r="N128" s="10" t="n"/>
-      <c r="O128" s="10" t="n"/>
+      <c r="E128" s="11" t="n"/>
+      <c r="F128" s="11" t="n"/>
+      <c r="G128" s="11" t="n"/>
+      <c r="H128" s="11" t="n"/>
+      <c r="I128" s="11" t="n"/>
+      <c r="J128" s="11" t="n"/>
+      <c r="K128" s="11" t="n"/>
+      <c r="L128" s="11" t="n"/>
+      <c r="M128" s="11" t="n"/>
+      <c r="N128" s="11" t="n"/>
+      <c r="O128" s="11" t="n"/>
       <c r="P128" s="23" t="n"/>
       <c r="Q128" s="23" t="n"/>
       <c r="R128" s="24" t="n"/>
@@ -3988,9 +4021,9 @@
       <c r="AC128" s="24" t="n"/>
       <c r="AD128" s="24" t="n"/>
       <c r="AE128" s="24" t="n"/>
-      <c r="AF128" s="10" t="n"/>
-      <c r="AG128" s="10" t="n"/>
-      <c r="AH128" s="10" t="n"/>
+      <c r="AF128" s="11" t="n"/>
+      <c r="AG128" s="11" t="n"/>
+      <c r="AH128" s="11" t="n"/>
       <c r="AI128" s="25" t="n"/>
       <c r="AJ128" s="25" t="n"/>
       <c r="AK128" s="25" t="n"/>
@@ -4012,17 +4045,17 @@
       <c r="D129" t="n">
         <v>40</v>
       </c>
-      <c r="E129" s="10" t="n"/>
-      <c r="F129" s="10" t="n"/>
-      <c r="G129" s="10" t="n"/>
-      <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="10" t="n"/>
-      <c r="K129" s="10" t="n"/>
-      <c r="L129" s="10" t="n"/>
-      <c r="M129" s="10" t="n"/>
-      <c r="N129" s="10" t="n"/>
-      <c r="O129" s="10" t="n"/>
+      <c r="E129" s="11" t="n"/>
+      <c r="F129" s="11" t="n"/>
+      <c r="G129" s="11" t="n"/>
+      <c r="H129" s="11" t="n"/>
+      <c r="I129" s="11" t="n"/>
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="11" t="n"/>
+      <c r="O129" s="11" t="n"/>
       <c r="P129" s="23" t="n"/>
       <c r="Q129" s="23" t="n"/>
       <c r="R129" s="24" t="n"/>
@@ -4039,9 +4072,9 @@
       <c r="AC129" s="24" t="n"/>
       <c r="AD129" s="24" t="n"/>
       <c r="AE129" s="24" t="n"/>
-      <c r="AF129" s="10" t="n"/>
-      <c r="AG129" s="10" t="n"/>
-      <c r="AH129" s="10" t="n"/>
+      <c r="AF129" s="11" t="n"/>
+      <c r="AG129" s="11" t="n"/>
+      <c r="AH129" s="11" t="n"/>
       <c r="AI129" s="25" t="n"/>
       <c r="AJ129" s="25" t="n"/>
       <c r="AK129" s="25" t="n"/>
@@ -4063,17 +4096,17 @@
       <c r="D130" t="n">
         <v>30</v>
       </c>
-      <c r="E130" s="10" t="n"/>
-      <c r="F130" s="10" t="n"/>
-      <c r="G130" s="10" t="n"/>
-      <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="10" t="n"/>
-      <c r="K130" s="10" t="n"/>
-      <c r="L130" s="10" t="n"/>
-      <c r="M130" s="10" t="n"/>
-      <c r="N130" s="10" t="n"/>
-      <c r="O130" s="10" t="n"/>
+      <c r="E130" s="11" t="n"/>
+      <c r="F130" s="11" t="n"/>
+      <c r="G130" s="11" t="n"/>
+      <c r="H130" s="11" t="n"/>
+      <c r="I130" s="11" t="n"/>
+      <c r="J130" s="11" t="n"/>
+      <c r="K130" s="11" t="n"/>
+      <c r="L130" s="11" t="n"/>
+      <c r="M130" s="11" t="n"/>
+      <c r="N130" s="11" t="n"/>
+      <c r="O130" s="11" t="n"/>
       <c r="P130" s="23" t="n"/>
       <c r="Q130" s="23" t="n"/>
       <c r="R130" s="24" t="n"/>
@@ -4090,9 +4123,9 @@
       <c r="AC130" s="24" t="n"/>
       <c r="AD130" s="24" t="n"/>
       <c r="AE130" s="24" t="n"/>
-      <c r="AF130" s="10" t="n"/>
-      <c r="AG130" s="10" t="n"/>
-      <c r="AH130" s="10" t="n"/>
+      <c r="AF130" s="11" t="n"/>
+      <c r="AG130" s="11" t="n"/>
+      <c r="AH130" s="11" t="n"/>
       <c r="AI130" s="25" t="n"/>
       <c r="AJ130" s="25" t="n"/>
       <c r="AK130" s="25" t="n"/>
@@ -4114,17 +4147,17 @@
       <c r="D131" t="n">
         <v>20</v>
       </c>
-      <c r="E131" s="10" t="n"/>
-      <c r="F131" s="10" t="n"/>
-      <c r="G131" s="10" t="n"/>
-      <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="n"/>
-      <c r="J131" s="10" t="n"/>
-      <c r="K131" s="10" t="n"/>
-      <c r="L131" s="10" t="n"/>
-      <c r="M131" s="10" t="n"/>
-      <c r="N131" s="10" t="n"/>
-      <c r="O131" s="10" t="n"/>
+      <c r="E131" s="11" t="n"/>
+      <c r="F131" s="11" t="n"/>
+      <c r="G131" s="11" t="n"/>
+      <c r="H131" s="11" t="n"/>
+      <c r="I131" s="11" t="n"/>
+      <c r="J131" s="11" t="n"/>
+      <c r="K131" s="11" t="n"/>
+      <c r="L131" s="11" t="n"/>
+      <c r="M131" s="11" t="n"/>
+      <c r="N131" s="11" t="n"/>
+      <c r="O131" s="11" t="n"/>
       <c r="P131" s="23" t="n"/>
       <c r="Q131" s="23" t="n"/>
       <c r="R131" s="24" t="n"/>
@@ -4141,9 +4174,9 @@
       <c r="AC131" s="24" t="n"/>
       <c r="AD131" s="24" t="n"/>
       <c r="AE131" s="24" t="n"/>
-      <c r="AF131" s="10" t="n"/>
-      <c r="AG131" s="10" t="n"/>
-      <c r="AH131" s="10" t="n"/>
+      <c r="AF131" s="11" t="n"/>
+      <c r="AG131" s="11" t="n"/>
+      <c r="AH131" s="11" t="n"/>
       <c r="AI131" s="25" t="n"/>
       <c r="AJ131" s="25" t="n"/>
       <c r="AK131" s="25" t="n"/>
@@ -4165,17 +4198,17 @@
       <c r="D132" t="n">
         <v>10</v>
       </c>
-      <c r="E132" s="10" t="n"/>
-      <c r="F132" s="10" t="n"/>
-      <c r="G132" s="10" t="n"/>
-      <c r="H132" s="10" t="n"/>
-      <c r="I132" s="10" t="n"/>
-      <c r="J132" s="10" t="n"/>
-      <c r="K132" s="10" t="n"/>
-      <c r="L132" s="10" t="n"/>
-      <c r="M132" s="10" t="n"/>
-      <c r="N132" s="10" t="n"/>
-      <c r="O132" s="10" t="n"/>
+      <c r="E132" s="11" t="n"/>
+      <c r="F132" s="11" t="n"/>
+      <c r="G132" s="11" t="n"/>
+      <c r="H132" s="11" t="n"/>
+      <c r="I132" s="11" t="n"/>
+      <c r="J132" s="11" t="n"/>
+      <c r="K132" s="11" t="n"/>
+      <c r="L132" s="11" t="n"/>
+      <c r="M132" s="11" t="n"/>
+      <c r="N132" s="11" t="n"/>
+      <c r="O132" s="11" t="n"/>
       <c r="P132" s="23" t="n"/>
       <c r="Q132" s="23" t="n"/>
       <c r="R132" s="24" t="n"/>
@@ -4192,9 +4225,9 @@
       <c r="AC132" s="24" t="n"/>
       <c r="AD132" s="24" t="n"/>
       <c r="AE132" s="24" t="n"/>
-      <c r="AF132" s="10" t="n"/>
-      <c r="AG132" s="10" t="n"/>
-      <c r="AH132" s="10" t="n"/>
+      <c r="AF132" s="11" t="n"/>
+      <c r="AG132" s="11" t="n"/>
+      <c r="AH132" s="11" t="n"/>
       <c r="AI132" s="25" t="n"/>
       <c r="AJ132" s="25" t="n"/>
       <c r="AK132" s="25" t="n"/>
@@ -4216,17 +4249,17 @@
       <c r="D133" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="10" t="n"/>
-      <c r="F133" s="10" t="n"/>
-      <c r="G133" s="10" t="n"/>
-      <c r="H133" s="10" t="n"/>
-      <c r="I133" s="10" t="n"/>
-      <c r="J133" s="10" t="n"/>
-      <c r="K133" s="10" t="n"/>
-      <c r="L133" s="10" t="n"/>
-      <c r="M133" s="10" t="n"/>
-      <c r="N133" s="10" t="n"/>
-      <c r="O133" s="10" t="n"/>
+      <c r="E133" s="11" t="n"/>
+      <c r="F133" s="11" t="n"/>
+      <c r="G133" s="11" t="n"/>
+      <c r="H133" s="11" t="n"/>
+      <c r="I133" s="11" t="n"/>
+      <c r="J133" s="11" t="n"/>
+      <c r="K133" s="11" t="n"/>
+      <c r="L133" s="11" t="n"/>
+      <c r="M133" s="11" t="n"/>
+      <c r="N133" s="11" t="n"/>
+      <c r="O133" s="11" t="n"/>
       <c r="P133" s="23" t="n"/>
       <c r="Q133" s="23" t="n"/>
       <c r="R133" s="24" t="n"/>
@@ -4243,9 +4276,9 @@
       <c r="AC133" s="24" t="n"/>
       <c r="AD133" s="24" t="n"/>
       <c r="AE133" s="24" t="n"/>
-      <c r="AF133" s="10" t="n"/>
-      <c r="AG133" s="10" t="n"/>
-      <c r="AH133" s="10" t="n"/>
+      <c r="AF133" s="11" t="n"/>
+      <c r="AG133" s="11" t="n"/>
+      <c r="AH133" s="11" t="n"/>
       <c r="AI133" s="25" t="n"/>
       <c r="AJ133" s="25" t="n"/>
       <c r="AK133" s="25" t="n"/>
@@ -4267,17 +4300,17 @@
       <c r="D134" t="n">
         <v>50</v>
       </c>
-      <c r="E134" s="10" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="10" t="n"/>
-      <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
-      <c r="J134" s="10" t="n"/>
-      <c r="K134" s="10" t="n"/>
-      <c r="L134" s="10" t="n"/>
-      <c r="M134" s="10" t="n"/>
-      <c r="N134" s="10" t="n"/>
-      <c r="O134" s="10" t="n"/>
+      <c r="E134" s="11" t="n"/>
+      <c r="F134" s="11" t="n"/>
+      <c r="G134" s="11" t="n"/>
+      <c r="H134" s="11" t="n"/>
+      <c r="I134" s="11" t="n"/>
+      <c r="J134" s="11" t="n"/>
+      <c r="K134" s="11" t="n"/>
+      <c r="L134" s="11" t="n"/>
+      <c r="M134" s="11" t="n"/>
+      <c r="N134" s="11" t="n"/>
+      <c r="O134" s="11" t="n"/>
       <c r="P134" s="23" t="n"/>
       <c r="Q134" s="23" t="n"/>
       <c r="R134" s="24" t="n"/>
@@ -4294,9 +4327,9 @@
       <c r="AC134" s="24" t="n"/>
       <c r="AD134" s="24" t="n"/>
       <c r="AE134" s="24" t="n"/>
-      <c r="AF134" s="10" t="n"/>
-      <c r="AG134" s="10" t="n"/>
-      <c r="AH134" s="10" t="n"/>
+      <c r="AF134" s="11" t="n"/>
+      <c r="AG134" s="11" t="n"/>
+      <c r="AH134" s="11" t="n"/>
       <c r="AI134" s="25" t="n"/>
       <c r="AJ134" s="25" t="n"/>
       <c r="AK134" s="25" t="n"/>
@@ -4318,17 +4351,17 @@
       <c r="D135" t="n">
         <v>40</v>
       </c>
-      <c r="E135" s="10" t="n"/>
-      <c r="F135" s="10" t="n"/>
-      <c r="G135" s="10" t="n"/>
-      <c r="H135" s="10" t="n"/>
-      <c r="I135" s="10" t="n"/>
-      <c r="J135" s="10" t="n"/>
-      <c r="K135" s="10" t="n"/>
-      <c r="L135" s="10" t="n"/>
-      <c r="M135" s="10" t="n"/>
-      <c r="N135" s="10" t="n"/>
-      <c r="O135" s="10" t="n"/>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+      <c r="G135" s="11" t="n"/>
+      <c r="H135" s="11" t="n"/>
+      <c r="I135" s="11" t="n"/>
+      <c r="J135" s="11" t="n"/>
+      <c r="K135" s="11" t="n"/>
+      <c r="L135" s="11" t="n"/>
+      <c r="M135" s="11" t="n"/>
+      <c r="N135" s="11" t="n"/>
+      <c r="O135" s="11" t="n"/>
       <c r="P135" s="23" t="n"/>
       <c r="Q135" s="23" t="n"/>
       <c r="R135" s="24" t="n"/>
@@ -4345,9 +4378,9 @@
       <c r="AC135" s="24" t="n"/>
       <c r="AD135" s="24" t="n"/>
       <c r="AE135" s="24" t="n"/>
-      <c r="AF135" s="10" t="n"/>
-      <c r="AG135" s="10" t="n"/>
-      <c r="AH135" s="10" t="n"/>
+      <c r="AF135" s="11" t="n"/>
+      <c r="AG135" s="11" t="n"/>
+      <c r="AH135" s="11" t="n"/>
       <c r="AI135" s="25" t="n"/>
       <c r="AJ135" s="25" t="n"/>
       <c r="AK135" s="25" t="n"/>
@@ -4369,17 +4402,17 @@
       <c r="D136" t="n">
         <v>30</v>
       </c>
-      <c r="E136" s="10" t="n"/>
-      <c r="F136" s="10" t="n"/>
-      <c r="G136" s="10" t="n"/>
-      <c r="H136" s="10" t="n"/>
-      <c r="I136" s="10" t="n"/>
-      <c r="J136" s="10" t="n"/>
-      <c r="K136" s="10" t="n"/>
-      <c r="L136" s="10" t="n"/>
-      <c r="M136" s="10" t="n"/>
-      <c r="N136" s="10" t="n"/>
-      <c r="O136" s="10" t="n"/>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
+      <c r="G136" s="11" t="n"/>
+      <c r="H136" s="11" t="n"/>
+      <c r="I136" s="11" t="n"/>
+      <c r="J136" s="11" t="n"/>
+      <c r="K136" s="11" t="n"/>
+      <c r="L136" s="11" t="n"/>
+      <c r="M136" s="11" t="n"/>
+      <c r="N136" s="11" t="n"/>
+      <c r="O136" s="11" t="n"/>
       <c r="P136" s="23" t="n"/>
       <c r="Q136" s="23" t="n"/>
       <c r="R136" s="24" t="n"/>
@@ -4396,9 +4429,9 @@
       <c r="AC136" s="24" t="n"/>
       <c r="AD136" s="24" t="n"/>
       <c r="AE136" s="24" t="n"/>
-      <c r="AF136" s="10" t="n"/>
-      <c r="AG136" s="10" t="n"/>
-      <c r="AH136" s="10" t="n"/>
+      <c r="AF136" s="11" t="n"/>
+      <c r="AG136" s="11" t="n"/>
+      <c r="AH136" s="11" t="n"/>
       <c r="AI136" s="25" t="n"/>
       <c r="AJ136" s="25" t="n"/>
       <c r="AK136" s="25" t="n"/>
@@ -4420,17 +4453,17 @@
       <c r="D137" t="n">
         <v>20</v>
       </c>
-      <c r="E137" s="10" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="10" t="n"/>
-      <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
-      <c r="J137" s="10" t="n"/>
-      <c r="K137" s="10" t="n"/>
-      <c r="L137" s="10" t="n"/>
-      <c r="M137" s="10" t="n"/>
-      <c r="N137" s="10" t="n"/>
-      <c r="O137" s="10" t="n"/>
+      <c r="E137" s="11" t="n"/>
+      <c r="F137" s="11" t="n"/>
+      <c r="G137" s="11" t="n"/>
+      <c r="H137" s="11" t="n"/>
+      <c r="I137" s="11" t="n"/>
+      <c r="J137" s="11" t="n"/>
+      <c r="K137" s="11" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="11" t="n"/>
+      <c r="N137" s="11" t="n"/>
+      <c r="O137" s="11" t="n"/>
       <c r="P137" s="23" t="n"/>
       <c r="Q137" s="23" t="n"/>
       <c r="R137" s="24" t="n"/>
@@ -4447,9 +4480,9 @@
       <c r="AC137" s="24" t="n"/>
       <c r="AD137" s="24" t="n"/>
       <c r="AE137" s="24" t="n"/>
-      <c r="AF137" s="10" t="n"/>
-      <c r="AG137" s="10" t="n"/>
-      <c r="AH137" s="10" t="n"/>
+      <c r="AF137" s="11" t="n"/>
+      <c r="AG137" s="11" t="n"/>
+      <c r="AH137" s="11" t="n"/>
       <c r="AI137" s="25" t="n"/>
       <c r="AJ137" s="25" t="n"/>
       <c r="AK137" s="25" t="n"/>
@@ -4471,17 +4504,17 @@
       <c r="D138" t="n">
         <v>10</v>
       </c>
-      <c r="E138" s="10" t="n"/>
-      <c r="F138" s="10" t="n"/>
-      <c r="G138" s="10" t="n"/>
-      <c r="H138" s="10" t="n"/>
-      <c r="I138" s="10" t="n"/>
-      <c r="J138" s="10" t="n"/>
-      <c r="K138" s="10" t="n"/>
-      <c r="L138" s="10" t="n"/>
-      <c r="M138" s="10" t="n"/>
-      <c r="N138" s="10" t="n"/>
-      <c r="O138" s="10" t="n"/>
+      <c r="E138" s="11" t="n"/>
+      <c r="F138" s="11" t="n"/>
+      <c r="G138" s="11" t="n"/>
+      <c r="H138" s="11" t="n"/>
+      <c r="I138" s="11" t="n"/>
+      <c r="J138" s="11" t="n"/>
+      <c r="K138" s="11" t="n"/>
+      <c r="L138" s="11" t="n"/>
+      <c r="M138" s="11" t="n"/>
+      <c r="N138" s="11" t="n"/>
+      <c r="O138" s="11" t="n"/>
       <c r="P138" s="23" t="n"/>
       <c r="Q138" s="23" t="n"/>
       <c r="R138" s="24" t="n"/>
@@ -4498,9 +4531,9 @@
       <c r="AC138" s="24" t="n"/>
       <c r="AD138" s="24" t="n"/>
       <c r="AE138" s="24" t="n"/>
-      <c r="AF138" s="10" t="n"/>
-      <c r="AG138" s="10" t="n"/>
-      <c r="AH138" s="10" t="n"/>
+      <c r="AF138" s="11" t="n"/>
+      <c r="AG138" s="11" t="n"/>
+      <c r="AH138" s="11" t="n"/>
       <c r="AI138" s="25" t="n"/>
       <c r="AJ138" s="25" t="n"/>
       <c r="AK138" s="25" t="n"/>
@@ -4522,17 +4555,17 @@
       <c r="D139" t="n">
         <v>0</v>
       </c>
-      <c r="E139" s="10" t="n"/>
-      <c r="F139" s="10" t="n"/>
-      <c r="G139" s="10" t="n"/>
-      <c r="H139" s="10" t="n"/>
-      <c r="I139" s="10" t="n"/>
-      <c r="J139" s="10" t="n"/>
-      <c r="K139" s="10" t="n"/>
-      <c r="L139" s="10" t="n"/>
-      <c r="M139" s="10" t="n"/>
-      <c r="N139" s="10" t="n"/>
-      <c r="O139" s="10" t="n"/>
+      <c r="E139" s="11" t="n"/>
+      <c r="F139" s="11" t="n"/>
+      <c r="G139" s="11" t="n"/>
+      <c r="H139" s="11" t="n"/>
+      <c r="I139" s="11" t="n"/>
+      <c r="J139" s="11" t="n"/>
+      <c r="K139" s="11" t="n"/>
+      <c r="L139" s="11" t="n"/>
+      <c r="M139" s="11" t="n"/>
+      <c r="N139" s="11" t="n"/>
+      <c r="O139" s="11" t="n"/>
       <c r="P139" s="23" t="n"/>
       <c r="Q139" s="23" t="n"/>
       <c r="R139" s="24" t="n"/>
@@ -4549,9 +4582,9 @@
       <c r="AC139" s="24" t="n"/>
       <c r="AD139" s="24" t="n"/>
       <c r="AE139" s="24" t="n"/>
-      <c r="AF139" s="10" t="n"/>
-      <c r="AG139" s="10" t="n"/>
-      <c r="AH139" s="10" t="n"/>
+      <c r="AF139" s="11" t="n"/>
+      <c r="AG139" s="11" t="n"/>
+      <c r="AH139" s="11" t="n"/>
       <c r="AI139" s="25" t="n"/>
       <c r="AJ139" s="25" t="n"/>
       <c r="AK139" s="25" t="n"/>
@@ -4573,17 +4606,17 @@
       <c r="D140" t="n">
         <v>40</v>
       </c>
-      <c r="E140" s="10" t="n"/>
-      <c r="F140" s="10" t="n"/>
-      <c r="G140" s="10" t="n"/>
-      <c r="H140" s="10" t="n"/>
-      <c r="I140" s="10" t="n"/>
-      <c r="J140" s="10" t="n"/>
-      <c r="K140" s="10" t="n"/>
-      <c r="L140" s="10" t="n"/>
-      <c r="M140" s="10" t="n"/>
-      <c r="N140" s="10" t="n"/>
-      <c r="O140" s="10" t="n"/>
+      <c r="E140" s="11" t="n"/>
+      <c r="F140" s="11" t="n"/>
+      <c r="G140" s="11" t="n"/>
+      <c r="H140" s="11" t="n"/>
+      <c r="I140" s="11" t="n"/>
+      <c r="J140" s="11" t="n"/>
+      <c r="K140" s="11" t="n"/>
+      <c r="L140" s="11" t="n"/>
+      <c r="M140" s="11" t="n"/>
+      <c r="N140" s="11" t="n"/>
+      <c r="O140" s="11" t="n"/>
       <c r="P140" s="23" t="n"/>
       <c r="Q140" s="23" t="n"/>
       <c r="R140" s="24" t="n"/>
@@ -4600,9 +4633,9 @@
       <c r="AC140" s="24" t="n"/>
       <c r="AD140" s="24" t="n"/>
       <c r="AE140" s="24" t="n"/>
-      <c r="AF140" s="10" t="n"/>
-      <c r="AG140" s="10" t="n"/>
-      <c r="AH140" s="10" t="n"/>
+      <c r="AF140" s="11" t="n"/>
+      <c r="AG140" s="11" t="n"/>
+      <c r="AH140" s="11" t="n"/>
       <c r="AI140" s="25" t="n"/>
       <c r="AJ140" s="25" t="n"/>
       <c r="AK140" s="25" t="n"/>
@@ -4624,17 +4657,17 @@
       <c r="D141" t="n">
         <v>30</v>
       </c>
-      <c r="E141" s="10" t="n"/>
-      <c r="F141" s="10" t="n"/>
-      <c r="G141" s="10" t="n"/>
-      <c r="H141" s="10" t="n"/>
-      <c r="I141" s="10" t="n"/>
-      <c r="J141" s="10" t="n"/>
-      <c r="K141" s="10" t="n"/>
-      <c r="L141" s="10" t="n"/>
-      <c r="M141" s="10" t="n"/>
-      <c r="N141" s="10" t="n"/>
-      <c r="O141" s="10" t="n"/>
+      <c r="E141" s="11" t="n"/>
+      <c r="F141" s="11" t="n"/>
+      <c r="G141" s="11" t="n"/>
+      <c r="H141" s="11" t="n"/>
+      <c r="I141" s="11" t="n"/>
+      <c r="J141" s="11" t="n"/>
+      <c r="K141" s="11" t="n"/>
+      <c r="L141" s="11" t="n"/>
+      <c r="M141" s="11" t="n"/>
+      <c r="N141" s="11" t="n"/>
+      <c r="O141" s="11" t="n"/>
       <c r="P141" s="23" t="n"/>
       <c r="Q141" s="23" t="n"/>
       <c r="R141" s="24" t="n"/>
@@ -4651,9 +4684,9 @@
       <c r="AC141" s="24" t="n"/>
       <c r="AD141" s="24" t="n"/>
       <c r="AE141" s="24" t="n"/>
-      <c r="AF141" s="10" t="n"/>
-      <c r="AG141" s="10" t="n"/>
-      <c r="AH141" s="10" t="n"/>
+      <c r="AF141" s="11" t="n"/>
+      <c r="AG141" s="11" t="n"/>
+      <c r="AH141" s="11" t="n"/>
       <c r="AI141" s="25" t="n"/>
       <c r="AJ141" s="25" t="n"/>
       <c r="AK141" s="25" t="n"/>
@@ -4675,17 +4708,17 @@
       <c r="D142" t="n">
         <v>20</v>
       </c>
-      <c r="E142" s="10" t="n"/>
-      <c r="F142" s="10" t="n"/>
-      <c r="G142" s="10" t="n"/>
-      <c r="H142" s="10" t="n"/>
-      <c r="I142" s="10" t="n"/>
-      <c r="J142" s="10" t="n"/>
-      <c r="K142" s="10" t="n"/>
-      <c r="L142" s="10" t="n"/>
-      <c r="M142" s="10" t="n"/>
-      <c r="N142" s="10" t="n"/>
-      <c r="O142" s="10" t="n"/>
+      <c r="E142" s="11" t="n"/>
+      <c r="F142" s="11" t="n"/>
+      <c r="G142" s="11" t="n"/>
+      <c r="H142" s="11" t="n"/>
+      <c r="I142" s="11" t="n"/>
+      <c r="J142" s="11" t="n"/>
+      <c r="K142" s="11" t="n"/>
+      <c r="L142" s="11" t="n"/>
+      <c r="M142" s="11" t="n"/>
+      <c r="N142" s="11" t="n"/>
+      <c r="O142" s="11" t="n"/>
       <c r="P142" s="23" t="n"/>
       <c r="Q142" s="23" t="n"/>
       <c r="R142" s="24" t="n"/>
@@ -4702,9 +4735,9 @@
       <c r="AC142" s="24" t="n"/>
       <c r="AD142" s="24" t="n"/>
       <c r="AE142" s="24" t="n"/>
-      <c r="AF142" s="10" t="n"/>
-      <c r="AG142" s="10" t="n"/>
-      <c r="AH142" s="10" t="n"/>
+      <c r="AF142" s="11" t="n"/>
+      <c r="AG142" s="11" t="n"/>
+      <c r="AH142" s="11" t="n"/>
       <c r="AI142" s="25" t="n"/>
       <c r="AJ142" s="25" t="n"/>
       <c r="AK142" s="25" t="n"/>
@@ -4726,17 +4759,17 @@
       <c r="D143" t="n">
         <v>10</v>
       </c>
-      <c r="E143" s="10" t="n"/>
-      <c r="F143" s="10" t="n"/>
-      <c r="G143" s="10" t="n"/>
-      <c r="H143" s="10" t="n"/>
-      <c r="I143" s="10" t="n"/>
-      <c r="J143" s="10" t="n"/>
-      <c r="K143" s="10" t="n"/>
-      <c r="L143" s="10" t="n"/>
-      <c r="M143" s="10" t="n"/>
-      <c r="N143" s="10" t="n"/>
-      <c r="O143" s="10" t="n"/>
+      <c r="E143" s="11" t="n"/>
+      <c r="F143" s="11" t="n"/>
+      <c r="G143" s="11" t="n"/>
+      <c r="H143" s="11" t="n"/>
+      <c r="I143" s="11" t="n"/>
+      <c r="J143" s="11" t="n"/>
+      <c r="K143" s="11" t="n"/>
+      <c r="L143" s="11" t="n"/>
+      <c r="M143" s="11" t="n"/>
+      <c r="N143" s="11" t="n"/>
+      <c r="O143" s="11" t="n"/>
       <c r="P143" s="23" t="n"/>
       <c r="Q143" s="23" t="n"/>
       <c r="R143" s="24" t="n"/>
@@ -4753,9 +4786,9 @@
       <c r="AC143" s="24" t="n"/>
       <c r="AD143" s="24" t="n"/>
       <c r="AE143" s="24" t="n"/>
-      <c r="AF143" s="10" t="n"/>
-      <c r="AG143" s="10" t="n"/>
-      <c r="AH143" s="10" t="n"/>
+      <c r="AF143" s="11" t="n"/>
+      <c r="AG143" s="11" t="n"/>
+      <c r="AH143" s="11" t="n"/>
       <c r="AI143" s="25" t="n"/>
       <c r="AJ143" s="25" t="n"/>
       <c r="AK143" s="25" t="n"/>
@@ -4777,17 +4810,17 @@
       <c r="D144" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="10" t="n"/>
-      <c r="F144" s="10" t="n"/>
-      <c r="G144" s="10" t="n"/>
-      <c r="H144" s="10" t="n"/>
-      <c r="I144" s="10" t="n"/>
-      <c r="J144" s="10" t="n"/>
-      <c r="K144" s="10" t="n"/>
-      <c r="L144" s="10" t="n"/>
-      <c r="M144" s="10" t="n"/>
-      <c r="N144" s="10" t="n"/>
-      <c r="O144" s="10" t="n"/>
+      <c r="E144" s="11" t="n"/>
+      <c r="F144" s="11" t="n"/>
+      <c r="G144" s="11" t="n"/>
+      <c r="H144" s="11" t="n"/>
+      <c r="I144" s="11" t="n"/>
+      <c r="J144" s="11" t="n"/>
+      <c r="K144" s="11" t="n"/>
+      <c r="L144" s="11" t="n"/>
+      <c r="M144" s="11" t="n"/>
+      <c r="N144" s="11" t="n"/>
+      <c r="O144" s="11" t="n"/>
       <c r="P144" s="23" t="n"/>
       <c r="Q144" s="23" t="n"/>
       <c r="R144" s="24" t="n"/>
@@ -4804,9 +4837,9 @@
       <c r="AC144" s="24" t="n"/>
       <c r="AD144" s="24" t="n"/>
       <c r="AE144" s="24" t="n"/>
-      <c r="AF144" s="10" t="n"/>
-      <c r="AG144" s="10" t="n"/>
-      <c r="AH144" s="10" t="n"/>
+      <c r="AF144" s="11" t="n"/>
+      <c r="AG144" s="11" t="n"/>
+      <c r="AH144" s="11" t="n"/>
       <c r="AI144" s="25" t="n"/>
       <c r="AJ144" s="25" t="n"/>
       <c r="AK144" s="25" t="n"/>
@@ -4828,17 +4861,17 @@
       <c r="D145" t="n">
         <v>30</v>
       </c>
-      <c r="E145" s="10" t="n"/>
-      <c r="F145" s="10" t="n"/>
-      <c r="G145" s="10" t="n"/>
-      <c r="H145" s="10" t="n"/>
-      <c r="I145" s="10" t="n"/>
-      <c r="J145" s="10" t="n"/>
-      <c r="K145" s="10" t="n"/>
-      <c r="L145" s="10" t="n"/>
-      <c r="M145" s="10" t="n"/>
-      <c r="N145" s="10" t="n"/>
-      <c r="O145" s="10" t="n"/>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="11" t="n"/>
+      <c r="G145" s="11" t="n"/>
+      <c r="H145" s="11" t="n"/>
+      <c r="I145" s="11" t="n"/>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
+      <c r="L145" s="11" t="n"/>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="11" t="n"/>
+      <c r="O145" s="11" t="n"/>
       <c r="P145" s="23" t="n"/>
       <c r="Q145" s="23" t="n"/>
       <c r="R145" s="24" t="n"/>
@@ -4855,9 +4888,9 @@
       <c r="AC145" s="24" t="n"/>
       <c r="AD145" s="24" t="n"/>
       <c r="AE145" s="24" t="n"/>
-      <c r="AF145" s="10" t="n"/>
-      <c r="AG145" s="10" t="n"/>
-      <c r="AH145" s="10" t="n"/>
+      <c r="AF145" s="11" t="n"/>
+      <c r="AG145" s="11" t="n"/>
+      <c r="AH145" s="11" t="n"/>
       <c r="AI145" s="25" t="n"/>
       <c r="AJ145" s="25" t="n"/>
       <c r="AK145" s="25" t="n"/>
@@ -4879,17 +4912,17 @@
       <c r="D146" t="n">
         <v>20</v>
       </c>
-      <c r="E146" s="10" t="n"/>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="10" t="n"/>
-      <c r="H146" s="10" t="n"/>
-      <c r="I146" s="10" t="n"/>
-      <c r="J146" s="10" t="n"/>
-      <c r="K146" s="10" t="n"/>
-      <c r="L146" s="10" t="n"/>
-      <c r="M146" s="10" t="n"/>
-      <c r="N146" s="10" t="n"/>
-      <c r="O146" s="10" t="n"/>
+      <c r="E146" s="11" t="n"/>
+      <c r="F146" s="11" t="n"/>
+      <c r="G146" s="11" t="n"/>
+      <c r="H146" s="11" t="n"/>
+      <c r="I146" s="11" t="n"/>
+      <c r="J146" s="11" t="n"/>
+      <c r="K146" s="11" t="n"/>
+      <c r="L146" s="11" t="n"/>
+      <c r="M146" s="11" t="n"/>
+      <c r="N146" s="11" t="n"/>
+      <c r="O146" s="11" t="n"/>
       <c r="P146" s="23" t="n"/>
       <c r="Q146" s="23" t="n"/>
       <c r="R146" s="24" t="n"/>
@@ -4906,9 +4939,9 @@
       <c r="AC146" s="24" t="n"/>
       <c r="AD146" s="24" t="n"/>
       <c r="AE146" s="24" t="n"/>
-      <c r="AF146" s="10" t="n"/>
-      <c r="AG146" s="10" t="n"/>
-      <c r="AH146" s="10" t="n"/>
+      <c r="AF146" s="11" t="n"/>
+      <c r="AG146" s="11" t="n"/>
+      <c r="AH146" s="11" t="n"/>
       <c r="AI146" s="25" t="n"/>
       <c r="AJ146" s="25" t="n"/>
       <c r="AK146" s="25" t="n"/>
@@ -4930,17 +4963,17 @@
       <c r="D147" t="n">
         <v>10</v>
       </c>
-      <c r="E147" s="10" t="n"/>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="10" t="n"/>
-      <c r="H147" s="10" t="n"/>
-      <c r="I147" s="10" t="n"/>
-      <c r="J147" s="10" t="n"/>
-      <c r="K147" s="10" t="n"/>
-      <c r="L147" s="10" t="n"/>
-      <c r="M147" s="10" t="n"/>
-      <c r="N147" s="10" t="n"/>
-      <c r="O147" s="10" t="n"/>
+      <c r="E147" s="11" t="n"/>
+      <c r="F147" s="11" t="n"/>
+      <c r="G147" s="11" t="n"/>
+      <c r="H147" s="11" t="n"/>
+      <c r="I147" s="11" t="n"/>
+      <c r="J147" s="11" t="n"/>
+      <c r="K147" s="11" t="n"/>
+      <c r="L147" s="11" t="n"/>
+      <c r="M147" s="11" t="n"/>
+      <c r="N147" s="11" t="n"/>
+      <c r="O147" s="11" t="n"/>
       <c r="P147" s="23" t="n"/>
       <c r="Q147" s="23" t="n"/>
       <c r="R147" s="24" t="n"/>
@@ -4957,9 +4990,9 @@
       <c r="AC147" s="24" t="n"/>
       <c r="AD147" s="24" t="n"/>
       <c r="AE147" s="24" t="n"/>
-      <c r="AF147" s="10" t="n"/>
-      <c r="AG147" s="10" t="n"/>
-      <c r="AH147" s="10" t="n"/>
+      <c r="AF147" s="11" t="n"/>
+      <c r="AG147" s="11" t="n"/>
+      <c r="AH147" s="11" t="n"/>
       <c r="AI147" s="25" t="n"/>
       <c r="AJ147" s="25" t="n"/>
       <c r="AK147" s="25" t="n"/>
@@ -4981,17 +5014,17 @@
       <c r="D148" t="n">
         <v>0</v>
       </c>
-      <c r="E148" s="10" t="n"/>
-      <c r="F148" s="10" t="n"/>
-      <c r="G148" s="10" t="n"/>
-      <c r="H148" s="10" t="n"/>
-      <c r="I148" s="10" t="n"/>
-      <c r="J148" s="10" t="n"/>
-      <c r="K148" s="10" t="n"/>
-      <c r="L148" s="10" t="n"/>
-      <c r="M148" s="10" t="n"/>
-      <c r="N148" s="10" t="n"/>
-      <c r="O148" s="10" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="11" t="n"/>
+      <c r="G148" s="11" t="n"/>
+      <c r="H148" s="11" t="n"/>
+      <c r="I148" s="11" t="n"/>
+      <c r="J148" s="11" t="n"/>
+      <c r="K148" s="11" t="n"/>
+      <c r="L148" s="11" t="n"/>
+      <c r="M148" s="11" t="n"/>
+      <c r="N148" s="11" t="n"/>
+      <c r="O148" s="11" t="n"/>
       <c r="P148" s="23" t="n"/>
       <c r="Q148" s="23" t="n"/>
       <c r="R148" s="24" t="n"/>
@@ -5008,9 +5041,9 @@
       <c r="AC148" s="24" t="n"/>
       <c r="AD148" s="24" t="n"/>
       <c r="AE148" s="24" t="n"/>
-      <c r="AF148" s="10" t="n"/>
-      <c r="AG148" s="10" t="n"/>
-      <c r="AH148" s="10" t="n"/>
+      <c r="AF148" s="11" t="n"/>
+      <c r="AG148" s="11" t="n"/>
+      <c r="AH148" s="11" t="n"/>
       <c r="AI148" s="25" t="n"/>
       <c r="AJ148" s="25" t="n"/>
       <c r="AK148" s="25" t="n"/>
@@ -5032,17 +5065,17 @@
       <c r="D149" t="n">
         <v>20</v>
       </c>
-      <c r="E149" s="10" t="n"/>
-      <c r="F149" s="10" t="n"/>
-      <c r="G149" s="10" t="n"/>
-      <c r="H149" s="10" t="n"/>
-      <c r="I149" s="10" t="n"/>
-      <c r="J149" s="10" t="n"/>
-      <c r="K149" s="10" t="n"/>
-      <c r="L149" s="10" t="n"/>
-      <c r="M149" s="10" t="n"/>
-      <c r="N149" s="10" t="n"/>
-      <c r="O149" s="10" t="n"/>
+      <c r="E149" s="11" t="n"/>
+      <c r="F149" s="11" t="n"/>
+      <c r="G149" s="11" t="n"/>
+      <c r="H149" s="11" t="n"/>
+      <c r="I149" s="11" t="n"/>
+      <c r="J149" s="11" t="n"/>
+      <c r="K149" s="11" t="n"/>
+      <c r="L149" s="11" t="n"/>
+      <c r="M149" s="11" t="n"/>
+      <c r="N149" s="11" t="n"/>
+      <c r="O149" s="11" t="n"/>
       <c r="P149" s="23" t="n"/>
       <c r="Q149" s="23" t="n"/>
       <c r="R149" s="24" t="n"/>
@@ -5059,9 +5092,9 @@
       <c r="AC149" s="24" t="n"/>
       <c r="AD149" s="24" t="n"/>
       <c r="AE149" s="24" t="n"/>
-      <c r="AF149" s="10" t="n"/>
-      <c r="AG149" s="10" t="n"/>
-      <c r="AH149" s="10" t="n"/>
+      <c r="AF149" s="11" t="n"/>
+      <c r="AG149" s="11" t="n"/>
+      <c r="AH149" s="11" t="n"/>
       <c r="AI149" s="25" t="n"/>
       <c r="AJ149" s="25" t="n"/>
       <c r="AK149" s="25" t="n"/>
@@ -5083,17 +5116,17 @@
       <c r="D150" t="n">
         <v>10</v>
       </c>
-      <c r="E150" s="10" t="n"/>
-      <c r="F150" s="10" t="n"/>
-      <c r="G150" s="10" t="n"/>
-      <c r="H150" s="10" t="n"/>
-      <c r="I150" s="10" t="n"/>
-      <c r="J150" s="10" t="n"/>
-      <c r="K150" s="10" t="n"/>
-      <c r="L150" s="10" t="n"/>
-      <c r="M150" s="10" t="n"/>
-      <c r="N150" s="10" t="n"/>
-      <c r="O150" s="10" t="n"/>
+      <c r="E150" s="11" t="n"/>
+      <c r="F150" s="11" t="n"/>
+      <c r="G150" s="11" t="n"/>
+      <c r="H150" s="11" t="n"/>
+      <c r="I150" s="11" t="n"/>
+      <c r="J150" s="11" t="n"/>
+      <c r="K150" s="11" t="n"/>
+      <c r="L150" s="11" t="n"/>
+      <c r="M150" s="11" t="n"/>
+      <c r="N150" s="11" t="n"/>
+      <c r="O150" s="11" t="n"/>
       <c r="P150" s="23" t="n"/>
       <c r="Q150" s="23" t="n"/>
       <c r="R150" s="24" t="n"/>
@@ -5110,9 +5143,9 @@
       <c r="AC150" s="24" t="n"/>
       <c r="AD150" s="24" t="n"/>
       <c r="AE150" s="24" t="n"/>
-      <c r="AF150" s="10" t="n"/>
-      <c r="AG150" s="10" t="n"/>
-      <c r="AH150" s="10" t="n"/>
+      <c r="AF150" s="11" t="n"/>
+      <c r="AG150" s="11" t="n"/>
+      <c r="AH150" s="11" t="n"/>
       <c r="AI150" s="25" t="n"/>
       <c r="AJ150" s="25" t="n"/>
       <c r="AK150" s="25" t="n"/>
@@ -5134,17 +5167,17 @@
       <c r="D151" t="n">
         <v>0</v>
       </c>
-      <c r="E151" s="10" t="n"/>
-      <c r="F151" s="10" t="n"/>
-      <c r="G151" s="10" t="n"/>
-      <c r="H151" s="10" t="n"/>
-      <c r="I151" s="10" t="n"/>
-      <c r="J151" s="10" t="n"/>
-      <c r="K151" s="10" t="n"/>
-      <c r="L151" s="10" t="n"/>
-      <c r="M151" s="10" t="n"/>
-      <c r="N151" s="10" t="n"/>
-      <c r="O151" s="10" t="n"/>
+      <c r="E151" s="11" t="n"/>
+      <c r="F151" s="11" t="n"/>
+      <c r="G151" s="11" t="n"/>
+      <c r="H151" s="11" t="n"/>
+      <c r="I151" s="11" t="n"/>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="n"/>
+      <c r="O151" s="11" t="n"/>
       <c r="P151" s="23" t="n"/>
       <c r="Q151" s="23" t="n"/>
       <c r="R151" s="24" t="n"/>
@@ -5161,9 +5194,9 @@
       <c r="AC151" s="24" t="n"/>
       <c r="AD151" s="24" t="n"/>
       <c r="AE151" s="24" t="n"/>
-      <c r="AF151" s="10" t="n"/>
-      <c r="AG151" s="10" t="n"/>
-      <c r="AH151" s="10" t="n"/>
+      <c r="AF151" s="11" t="n"/>
+      <c r="AG151" s="11" t="n"/>
+      <c r="AH151" s="11" t="n"/>
       <c r="AI151" s="25" t="n"/>
       <c r="AJ151" s="25" t="n"/>
       <c r="AK151" s="25" t="n"/>
@@ -5185,17 +5218,17 @@
       <c r="D152" t="n">
         <v>10</v>
       </c>
-      <c r="E152" s="10" t="n"/>
-      <c r="F152" s="10" t="n"/>
-      <c r="G152" s="10" t="n"/>
-      <c r="H152" s="10" t="n"/>
-      <c r="I152" s="10" t="n"/>
-      <c r="J152" s="10" t="n"/>
-      <c r="K152" s="10" t="n"/>
-      <c r="L152" s="10" t="n"/>
-      <c r="M152" s="10" t="n"/>
-      <c r="N152" s="10" t="n"/>
-      <c r="O152" s="10" t="n"/>
+      <c r="E152" s="11" t="n"/>
+      <c r="F152" s="11" t="n"/>
+      <c r="G152" s="11" t="n"/>
+      <c r="H152" s="11" t="n"/>
+      <c r="I152" s="11" t="n"/>
+      <c r="J152" s="11" t="n"/>
+      <c r="K152" s="11" t="n"/>
+      <c r="L152" s="11" t="n"/>
+      <c r="M152" s="11" t="n"/>
+      <c r="N152" s="11" t="n"/>
+      <c r="O152" s="11" t="n"/>
       <c r="P152" s="23" t="n"/>
       <c r="Q152" s="23" t="n"/>
       <c r="R152" s="24" t="n"/>
@@ -5212,9 +5245,9 @@
       <c r="AC152" s="24" t="n"/>
       <c r="AD152" s="24" t="n"/>
       <c r="AE152" s="24" t="n"/>
-      <c r="AF152" s="10" t="n"/>
-      <c r="AG152" s="10" t="n"/>
-      <c r="AH152" s="10" t="n"/>
+      <c r="AF152" s="11" t="n"/>
+      <c r="AG152" s="11" t="n"/>
+      <c r="AH152" s="11" t="n"/>
       <c r="AI152" s="25" t="n"/>
       <c r="AJ152" s="25" t="n"/>
       <c r="AK152" s="25" t="n"/>
@@ -5236,17 +5269,17 @@
       <c r="D153" t="n">
         <v>0</v>
       </c>
-      <c r="E153" s="10" t="n"/>
-      <c r="F153" s="10" t="n"/>
-      <c r="G153" s="10" t="n"/>
-      <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="n"/>
-      <c r="J153" s="10" t="n"/>
-      <c r="K153" s="10" t="n"/>
-      <c r="L153" s="10" t="n"/>
-      <c r="M153" s="10" t="n"/>
-      <c r="N153" s="10" t="n"/>
-      <c r="O153" s="10" t="n"/>
+      <c r="E153" s="11" t="n"/>
+      <c r="F153" s="11" t="n"/>
+      <c r="G153" s="11" t="n"/>
+      <c r="H153" s="11" t="n"/>
+      <c r="I153" s="11" t="n"/>
+      <c r="J153" s="11" t="n"/>
+      <c r="K153" s="11" t="n"/>
+      <c r="L153" s="11" t="n"/>
+      <c r="M153" s="11" t="n"/>
+      <c r="N153" s="11" t="n"/>
+      <c r="O153" s="11" t="n"/>
       <c r="P153" s="23" t="n"/>
       <c r="Q153" s="23" t="n"/>
       <c r="R153" s="24" t="n"/>
@@ -5263,9 +5296,9 @@
       <c r="AC153" s="24" t="n"/>
       <c r="AD153" s="24" t="n"/>
       <c r="AE153" s="24" t="n"/>
-      <c r="AF153" s="10" t="n"/>
-      <c r="AG153" s="10" t="n"/>
-      <c r="AH153" s="10" t="n"/>
+      <c r="AF153" s="11" t="n"/>
+      <c r="AG153" s="11" t="n"/>
+      <c r="AH153" s="11" t="n"/>
       <c r="AI153" s="25" t="n"/>
       <c r="AJ153" s="25" t="n"/>
       <c r="AK153" s="25" t="n"/>
@@ -5287,17 +5320,17 @@
       <c r="D154" t="n">
         <v>0</v>
       </c>
-      <c r="E154" s="10" t="n"/>
-      <c r="F154" s="10" t="n"/>
-      <c r="G154" s="10" t="n"/>
-      <c r="H154" s="10" t="n"/>
-      <c r="I154" s="10" t="n"/>
-      <c r="J154" s="10" t="n"/>
-      <c r="K154" s="10" t="n"/>
-      <c r="L154" s="10" t="n"/>
-      <c r="M154" s="10" t="n"/>
-      <c r="N154" s="10" t="n"/>
-      <c r="O154" s="10" t="n"/>
+      <c r="E154" s="11" t="n"/>
+      <c r="F154" s="11" t="n"/>
+      <c r="G154" s="11" t="n"/>
+      <c r="H154" s="11" t="n"/>
+      <c r="I154" s="11" t="n"/>
+      <c r="J154" s="11" t="n"/>
+      <c r="K154" s="11" t="n"/>
+      <c r="L154" s="11" t="n"/>
+      <c r="M154" s="11" t="n"/>
+      <c r="N154" s="11" t="n"/>
+      <c r="O154" s="11" t="n"/>
       <c r="P154" s="23" t="n"/>
       <c r="Q154" s="23" t="n"/>
       <c r="R154" s="24" t="n"/>
@@ -5314,9 +5347,9 @@
       <c r="AC154" s="24" t="n"/>
       <c r="AD154" s="24" t="n"/>
       <c r="AE154" s="24" t="n"/>
-      <c r="AF154" s="10" t="n"/>
-      <c r="AG154" s="10" t="n"/>
-      <c r="AH154" s="10" t="n"/>
+      <c r="AF154" s="11" t="n"/>
+      <c r="AG154" s="11" t="n"/>
+      <c r="AH154" s="11" t="n"/>
       <c r="AI154" s="25" t="n"/>
       <c r="AJ154" s="25" t="n"/>
       <c r="AK154" s="25" t="n"/>
@@ -5324,6 +5357,35 @@
       <c r="AM154" s="24" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="הון עצמי נוסף: מספר בין 0 ל־500,000" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>500000</formula2>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="0 (לא) או 1 (כן)" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="0 (לא) או 1 (כן)" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="בנק: a, b, c או d" type="list">
+      <formula1>"a,b,c,d"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="משקולת: מספר שלם בין 0 ל־100" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="משקולת: מספר שלם בין 0 ל־100" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ערך לא תקין" error="משקולת: מספר שלם בין 0 ל־100" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -5398,13 +5460,23 @@
           <t>כמה מועמדים ברשת</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17">
+        <f>'מנוע'!$B$59</f>
         <v>66</v>
       </c>
-      <c r="D5" s="16" t="n"/>
+      <c r="C5" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="D5" s="17">
+        <f>IF(ISNUMBER(B5),B5-C5,"")</f>
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
         <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <f>IF(ISNUMBER(D5),IF(ABS(D5)&lt;=E5,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="6">
@@ -5413,13 +5485,23 @@
           <t>כמה אפשריים</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17">
+        <f>'מנוע'!$B$60</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="16" t="n"/>
+      <c r="D6" s="17">
+        <f>IF(ISNUMBER(B6),B6-C6,"")</f>
+        <v>-14</v>
+      </c>
       <c r="E6" t="n">
         <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(ISNUMBER(D6),IF(ABS(D6)&lt;=E6,"✓","✗"),"✗")</f>
+        <v>✗</v>
       </c>
     </row>
     <row r="7">
@@ -5428,13 +5510,23 @@
           <t>כמה יעילים</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17">
+        <f>'מנוע'!$B$61</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="16" t="n"/>
+      <c r="D7" s="17">
+        <f>IF(ISNUMBER(B7),B7-C7,"")</f>
+        <v>-6</v>
+      </c>
       <c r="E7" t="n">
         <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(ISNUMBER(D7),IF(ABS(D7)&lt;=E7,"✓","✗"),"✗")</f>
+        <v>✗</v>
       </c>
     </row>
     <row r="8">
@@ -5443,13 +5535,20 @@
           <t>המועמד שנבחר</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="str">
+        <f>'מנוע'!$B$62</f>
+        <v>אין מועמד אפשרי</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>g40-0-60</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="F8" t="str">
+        <f>IF(B8=C8,"✓","✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5457,14 +5556,24 @@
           <t>ההחזר הראשון של הנבחר</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n">
+      <c r="B9" s="10" t="str">
+        <f>'מנוע'!$B$63</f>
+        <v/>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>7941.62</v>
       </c>
-      <c r="D9" s="17" t="n"/>
+      <c r="D9" s="10" t="str">
+        <f>IF(ISNUMBER(B9),B9-C9,"")</f>
+        <v/>
+      </c>
       <c r="E9" t="n">
         <v>0.05</v>
       </c>
+      <c r="F9" t="str">
+        <f>IF(ISNUMBER(D9),IF(ABS(D9)&lt;=E9,"✓","✗"),"✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5472,14 +5581,24 @@
           <t>סך התשלומים של הנבחר</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n">
+      <c r="B10" s="10" t="str">
+        <f>'מנוע'!$B$64</f>
+        <v/>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>2858982.61</v>
       </c>
-      <c r="D10" s="17" t="n"/>
+      <c r="D10" s="10" t="str">
+        <f>IF(ISNUMBER(B10),B10-C10,"")</f>
+        <v/>
+      </c>
       <c r="E10" t="n">
         <v>6</v>
       </c>
+      <c r="F10" t="str">
+        <f>IF(ISNUMBER(D10),IF(ABS(D10)&lt;=E10,"✓","✗"),"✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5487,14 +5606,24 @@
           <t>החשיפה של הנבחר</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n">
-        <v>1031.61</v>
-      </c>
-      <c r="D11" s="17" t="n"/>
+      <c r="B11" s="10" t="str">
+        <f>'מנוע'!$B$65</f>
+        <v/>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1030.73</v>
+      </c>
+      <c r="D11" s="10" t="str">
+        <f>IF(ISNUMBER(B11),B11-C11,"")</f>
+        <v/>
+      </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
+      <c r="F11" t="str">
+        <f>IF(ISNUMBER(D11),IF(ABS(D11)&lt;=E11,"✓","✗"),"✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5502,13 +5631,23 @@
           <t>נפסלו: סכום המסלולים שווה להלוואה</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="16" t="n"/>
+      <c r="B12" s="17">
+        <f>'מנוע'!$B$72</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17">
+        <f>IF(ISNUMBER(B12),B12-C12,"")</f>
+        <v>0</v>
+      </c>
       <c r="E12" t="n">
         <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(ISNUMBER(D12),IF(ABS(D12)&lt;=E12,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="13">
@@ -5517,13 +5656,23 @@
           <t>נפסלו: ההון העצמי קיים</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16" t="n"/>
+      <c r="B13" s="17">
+        <f>'מנוע'!$B$73</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <f>IF(ISNUMBER(B13),B13-C13,"")</f>
+        <v>0</v>
+      </c>
       <c r="E13" t="n">
         <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(ISNUMBER(D13),IF(ABS(D13)&lt;=E13,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="14">
@@ -5532,13 +5681,23 @@
           <t>נפסלו: שיעור מימון עד התקרה</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="16" t="n"/>
+      <c r="B14" s="17">
+        <f>'מנוע'!$B$74</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17">
+        <f>IF(ISNUMBER(B14),B14-C14,"")</f>
+        <v>0</v>
+      </c>
       <c r="E14" t="n">
         <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(ISNUMBER(D14),IF(ABS(D14)&lt;=E14,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="15">
@@ -5547,13 +5706,23 @@
           <t>נפסלו: יחס החזר עד 50%</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16" t="n"/>
+      <c r="B15" s="17">
+        <f>'מנוע'!$B$75</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="17">
+        <f>IF(ISNUMBER(B15),B15-C15,"")</f>
+        <v>0</v>
+      </c>
       <c r="E15" t="n">
         <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <f>IF(ISNUMBER(D15),IF(ABS(D15)&lt;=E15,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="16">
@@ -5562,13 +5731,23 @@
           <t>נפסלו: לפחות שליש בריבית קבועה</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17">
+        <f>'מנוע'!$B$76</f>
+        <v>1</v>
+      </c>
+      <c r="C16" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="D16" s="16" t="n"/>
+      <c r="D16" s="17">
+        <f>IF(ISNUMBER(B16),B16-C16,"")</f>
+        <v>-37</v>
+      </c>
       <c r="E16" t="n">
         <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(ISNUMBER(D16),IF(ABS(D16)&lt;=E16,"✓","✗"),"✗")</f>
+        <v>✗</v>
       </c>
     </row>
     <row r="17">
@@ -5577,13 +5756,23 @@
           <t>נפסלו: עד 30 שנה</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="16" t="n"/>
+      <c r="B17" s="17">
+        <f>'מנוע'!$B$77</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17">
+        <f>IF(ISNUMBER(B17),B17-C17,"")</f>
+        <v>0</v>
+      </c>
       <c r="E17" t="n">
         <v>0</v>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(ISNUMBER(D17),IF(ABS(D17)&lt;=E17,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="18">
@@ -5592,13 +5781,23 @@
           <t>נפסלו: יחס ההחזר עד הקו של הבנק</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="16" t="n"/>
+      <c r="B18" s="17">
+        <f>'מנוע'!$B$78</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="17">
+        <f>IF(ISNUMBER(B18),B18-C18,"")</f>
+        <v>0</v>
+      </c>
       <c r="E18" t="n">
         <v>0</v>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(ISNUMBER(D18),IF(ABS(D18)&lt;=E18,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="19">
@@ -5607,13 +5806,23 @@
           <t>נפסלו: שיעור המימון עד הקו של הבנק</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="16" t="n"/>
+      <c r="B19" s="17">
+        <f>'מנוע'!$B$79</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
+        <f>IF(ISNUMBER(B19),B19-C19,"")</f>
+        <v>0</v>
+      </c>
       <c r="E19" t="n">
         <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <f>IF(ISNUMBER(D19),IF(ABS(D19)&lt;=E19,"✓","✗"),"✗")</f>
+        <v>✓</v>
       </c>
     </row>
     <row r="20">
@@ -5622,13 +5831,23 @@
           <t>נפסלו: ההחזר עד המרבי שהלקוח קבע</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17">
+        <f>'מנוע'!$B$80</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="16" t="n"/>
+      <c r="D20" s="17">
+        <f>IF(ISNUMBER(B20),B20-C20,"")</f>
+        <v>-1</v>
+      </c>
       <c r="E20" t="n">
         <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <f>IF(ISNUMBER(D20),IF(ABS(D20)&lt;=E20,"✓","✗"),"✗")</f>
+        <v>✗</v>
       </c>
     </row>
     <row r="21">
@@ -5637,13 +5856,23 @@
           <t>נפסלו: יחס ההחזר עד יעד הלקוח</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17">
+        <f>'מנוע'!$B$81</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="D21" s="16" t="n"/>
+      <c r="D21" s="17">
+        <f>IF(ISNUMBER(B21),B21-C21,"")</f>
+        <v>-31</v>
+      </c>
       <c r="E21" t="n">
         <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(ISNUMBER(D21),IF(ABS(D21)&lt;=E21,"✓","✗"),"✗")</f>
+        <v>✗</v>
       </c>
     </row>
     <row r="22">
@@ -5652,14 +5881,24 @@
           <t>הפער בהחזר הראשון: הצעה מול אומדן</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n">
+      <c r="B22" s="10">
+        <f>'מנוע'!$F$15</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D22" s="17" t="n"/>
+      <c r="D22" s="10" t="str">
+        <f>IF(ISNUMBER(B22),B22-C22,"")</f>
+        <v/>
+      </c>
       <c r="E22" t="n">
         <v>0.05</v>
       </c>
+      <c r="F22" t="str">
+        <f>IF(ISNUMBER(D22),IF(ABS(D22)&lt;=E22,"✓","✗"),"✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5667,14 +5906,24 @@
           <t>הפער בסך התשלומים: הצעה מול אומדן</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n">
+      <c r="B23" s="10">
+        <f>'מנוע'!$F$18</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="10" t="n">
         <v>-177.72</v>
       </c>
-      <c r="D23" s="17" t="n"/>
+      <c r="D23" s="10" t="str">
+        <f>IF(ISNUMBER(B23),B23-C23,"")</f>
+        <v/>
+      </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
+      <c r="F23" t="str">
+        <f>IF(ISNUMBER(D23),IF(ABS(D23)&lt;=E23,"✓","✗"),"✗")</f>
+        <v>✗</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5684,10 +5933,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>מלאו את הרשת, ואז כאן יופיע ✓.</t>
-        </is>
+      <c r="A26" s="3" t="str">
+        <f>IF(COUNTIF(F5:F23,"✗")=0,"✓ הכול בטווח","✗ יש פערים: בדקו את הנוסחאות או את הקלט")</f>
+        <v>✗ יש פערים: בדקו את הנוסחאות או את הקלט</v>
       </c>
     </row>
   </sheetData>
@@ -5701,7 +5949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -5738,7 +5986,7 @@
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>1 — מיצוב: בתאים B18 עד B21 בחרו הון עצמי נוסף, סגירת הלוואת הרכב, הורה וכנס. ההלוואה, שיעור המימון והכנסה הפנויה מתעדכנים (שורות 45 עד 56).</t>
+          <t>1 — מיצוב: בתאים B18 עד B21 בחרו הון עצמי נוסף, סגירת הלוואת הרכב, הורה ובנק. ההלוואה, שיעור המימון והכנסה הפנויה מתעדכנים (שורות 45 עד 56).</t>
         </is>
       </c>
     </row>
@@ -5752,7 +6000,7 @@
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>3 — חיפוש: הרשת היא כל התמהילים בצעדים של 10 אחוזים (66). אין להוסיף שורות: מרחב החיפוש הוא מה שנבדק.</t>
+          <t>3 — חיפוש: הרשת היא כל התמהילים בצעדים של 10 אחוזים (66). אין להוסיף שורות: מרחב החיפוש הוא מה שנבדק. שורת הרשת הראשונה (89) מלאה בכל העמודות כדוגמה. עמדו על כותרת של עמודה כדי לקרוא מה היא עושה (בכותרות עם הערה), העתיקו את השורה למטה עד שורה 154, ובדקו שהתוצאות בשורות 59 עד 69 התמלאו.</t>
         </is>
       </c>
     </row>
@@ -5787,40 +6035,47 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>8 — בדיקה מול הצעת בנק: בתאים E4 עד F18 יש הצעה לדוגמה של בנק בדוי. האומדן הוא המחירון של הבנק; ההצעה היא מה שהוא כתב. הפער נמדד בהחזר הראשון ובסך התשלומים.</t>
+          <t>8 — בדיקה מול הצעת בנק: בתאים E4 עד F11 יש הצעה לדוגמה של בנק בדוי. האומדן הוא המחירון של הבנק; ההצעה היא מה שהוא כתב. הפער נמדד בהחזר הראשון ובסך התשלומים.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>התא F13 מלא כדוגמה, ו־F14 עד F18 ריקים: מלאו אותם בעצמכם. F13 הוא ההחזר הראשון של האומדן: =IF($F$6&gt;0,ROUND(-PMT(INDEX($C$28:$C$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$6/100,2)),2),0)+IF($F$7&gt;0,ROUND(-PMT(INDEX($D$28:$D$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$7/100,2)),2),0)+IF($F$8&gt;0,ROUND(-PMT(INDEX($E$28:$E$31,MATCH($F$5,$A$28:$A$31,0))/1200,$B$39,ROUND(($B$5-$B$6)*$F$8/100,2)),2),0). ב־F14 אותו חישוב עם ריביות ההצעה (F9 עד F11), F15 הוא F14 פחות F13, ו־F16 עד F18 הם אותו דבר לסך התשלומים: בלי ROUND, כפול מספר החודשים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>הלשונית ״בדיקה״</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>היא משווה את הגיליון למנוע של הקורס לקלט ההתחלתי. הסבילות היא כמה שקלים, כי הגיליון לא מעגל כל ריבית חודשית.</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>היא משווה את הגיליון למנוע של הקורס לקלט ההתחלתי. הסבילות היא כמה שקלים, כי הגיליון לא מעגל כל ריבית חודשית. בתבנית היא מתעדכנת בזמן שאתם ממלאים: עמודה C היא התוצאות של המנוע, כך שאפשר להציץ בה בסוף, וכשהכול מתאים יופיע ✓ בתחתית.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Excel ו־Google Sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>בחלק מההגדרות האזוריות מפרידים בין ארגומנטים בנקודה־פסיק (;). הגיליון משתמש בפונקציות PMT, SUMPRODUCT, COUNTIFS ו־INDEX: הכול קיים גם ב־Google Sheets.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>בחלק מההגדרות האזוריות מפרידים בין ארגומנטים בנקודה־פסיק (;). הגיליון משתמש בפונקציות PMT, SUMPRODUCT, COUNTIFS ו־INDEX: הכול קיים גם ב־Google Sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>שינוי בחירה ישנה את התוצאות, וגם את הבדיקה: היא נכונה לקלט ההתחלתי בלבד.</t>
         </is>

--- a/public/downloads/engine-workshop-template.xlsx
+++ b/public/downloads/engine-workshop-template.xlsx
@@ -5618,7 +5618,7 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="F11" t="str">
         <f>IF(ISNUMBER(D11),IF(ABS(D11)&lt;=E11,"✓","✗"),"✗")</f>
@@ -5928,7 +5928,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>הגיליון מקרב את המנוע: הוא מחשב החזר מדויק (בלי עיגול כל ריבית חודשית), והמנוע מעגל כל חודש לאגורה. בסך התשלומים הפער עד כמה שקלים. בחשיפה הפער עד כעשרה שקלים, כי במנוע התשלום האחרון סוגר את היתרה, והוא גבוה בכמה שקלים מהתשלום הקבוע. הבחירה של התמהיל לא מושפעת.</t>
+          <t>הגיליון מקרב את המנוע: הוא מחשב החזר מדויק (בלי עיגול כל ריבית חודשית), והמנוע מעגל כל חודש לאגורה. בסך התשלומים הפער עד כמה שקלים, כי במנוע התשלום האחרון סוגר את היתרה והוא שונה בכמה שקלים מהקבוע. בחשיפה אין פער של ממש, כי המנוע לא סופר את התשלום האחרון בהחזר הגבוה. הבחירה של התמהיל לא מושפעת.</t>
         </is>
       </c>
     </row>
